--- a/research/traditional_assets/database/data/oman/oman_apparel.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_apparel.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1051621964902568</v>
+        <v>0.1050427031955214</v>
       </c>
       <c r="C2">
-        <v>6.813173200176773</v>
+        <v>6.754535081271712</v>
       </c>
       <c r="D2">
-        <v>6.417173200176773</v>
+        <v>6.425405081271712</v>
       </c>
       <c r="E2">
-        <v>-0.8070000000000001</v>
+        <v>-0.7401300000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.06687</v>
       </c>
       <c r="G2">
         <v>0.396</v>
@@ -1451,28 +1451,28 @@
         <v>1.33</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.003363561</v>
       </c>
       <c r="N2">
-        <v>1.33</v>
+        <v>1.326636439</v>
       </c>
       <c r="O2">
-        <v>0.1995</v>
+        <v>0.19899546585</v>
       </c>
       <c r="P2">
-        <v>1.1305</v>
+        <v>1.12764097315</v>
       </c>
       <c r="Q2">
-        <v>1.2905</v>
+        <v>1.28764097315</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1051621964902568</v>
+        <v>0.1056718719146681</v>
       </c>
       <c r="T2">
-        <v>0.7736884202461267</v>
+        <v>0.7803311996118762</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>395.4142648223119</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1050427031955214</v>
+        <v>0.104923209900786</v>
       </c>
       <c r="C3">
-        <v>6.754535081271712</v>
+        <v>6.695918109031281</v>
       </c>
       <c r="D3">
-        <v>6.425405081271712</v>
+        <v>6.433658109031281</v>
       </c>
       <c r="E3">
-        <v>-0.7401300000000001</v>
+        <v>-0.6732600000000001</v>
       </c>
       <c r="F3">
-        <v>0.06687</v>
+        <v>0.13374</v>
       </c>
       <c r="G3">
         <v>0.396</v>
@@ -1533,28 +1533,28 @@
         <v>1.33</v>
       </c>
       <c r="M3">
-        <v>0.003363561</v>
+        <v>0.006727121999999999</v>
       </c>
       <c r="N3">
-        <v>1.326636439</v>
+        <v>1.323272878</v>
       </c>
       <c r="O3">
-        <v>0.19899546585</v>
+        <v>0.1984909317</v>
       </c>
       <c r="P3">
-        <v>1.12764097315</v>
+        <v>1.1247819463</v>
       </c>
       <c r="Q3">
-        <v>1.28764097315</v>
+        <v>1.2847819463</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1056718719146681</v>
+        <v>0.1061919488783531</v>
       </c>
       <c r="T3">
-        <v>0.7803311996118762</v>
+        <v>0.7871095459034576</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>395.4142648223119</v>
+        <v>197.7071324111559</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.104923209900786</v>
+        <v>0.1048037166060506</v>
       </c>
       <c r="C4">
-        <v>6.695918109031281</v>
+        <v>6.637322365044955</v>
       </c>
       <c r="D4">
-        <v>6.433658109031281</v>
+        <v>6.441932365044956</v>
       </c>
       <c r="E4">
-        <v>-0.6732600000000001</v>
+        <v>-0.60639</v>
       </c>
       <c r="F4">
-        <v>0.13374</v>
+        <v>0.20061</v>
       </c>
       <c r="G4">
         <v>0.396</v>
@@ -1615,28 +1615,28 @@
         <v>1.33</v>
       </c>
       <c r="M4">
-        <v>0.006727121999999999</v>
+        <v>0.010090683</v>
       </c>
       <c r="N4">
-        <v>1.323272878</v>
+        <v>1.319909317</v>
       </c>
       <c r="O4">
-        <v>0.1984909317</v>
+        <v>0.19798639755</v>
       </c>
       <c r="P4">
-        <v>1.1247819463</v>
+        <v>1.12192291945</v>
       </c>
       <c r="Q4">
-        <v>1.2847819463</v>
+        <v>1.28192291945</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1061919488783531</v>
+        <v>0.1067227490784027</v>
       </c>
       <c r="T4">
-        <v>0.7871095459034576</v>
+        <v>0.7940276519123908</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>197.7071324111559</v>
+        <v>131.8047549407706</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1048037166060506</v>
+        <v>0.1046842233113152</v>
       </c>
       <c r="C5">
-        <v>6.637322365044955</v>
+        <v>6.578747931322463</v>
       </c>
       <c r="D5">
-        <v>6.441932365044956</v>
+        <v>6.450227931322464</v>
       </c>
       <c r="E5">
-        <v>-0.60639</v>
+        <v>-0.53952</v>
       </c>
       <c r="F5">
-        <v>0.20061</v>
+        <v>0.26748</v>
       </c>
       <c r="G5">
         <v>0.396</v>
@@ -1697,28 +1697,28 @@
         <v>1.33</v>
       </c>
       <c r="M5">
-        <v>0.010090683</v>
+        <v>0.013454244</v>
       </c>
       <c r="N5">
-        <v>1.319909317</v>
+        <v>1.316545756</v>
       </c>
       <c r="O5">
-        <v>0.19798639755</v>
+        <v>0.1974818634</v>
       </c>
       <c r="P5">
-        <v>1.12192291945</v>
+        <v>1.1190638926</v>
       </c>
       <c r="Q5">
-        <v>1.28192291945</v>
+        <v>1.2790638926</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1067227490784027</v>
+        <v>0.1072646076159534</v>
       </c>
       <c r="T5">
-        <v>0.7940276519123908</v>
+        <v>0.8010898851298437</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>131.8047549407706</v>
+        <v>98.85356620557796</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1046842233113152</v>
+        <v>0.1045647300165798</v>
       </c>
       <c r="C6">
-        <v>6.578747931322463</v>
+        <v>6.520194890296519</v>
       </c>
       <c r="D6">
-        <v>6.450227931322464</v>
+        <v>6.458544890296519</v>
       </c>
       <c r="E6">
-        <v>-0.53952</v>
+        <v>-0.47265</v>
       </c>
       <c r="F6">
-        <v>0.26748</v>
+        <v>0.33435</v>
       </c>
       <c r="G6">
         <v>0.396</v>
@@ -1779,28 +1779,28 @@
         <v>1.33</v>
       </c>
       <c r="M6">
-        <v>0.013454244</v>
+        <v>0.016817805</v>
       </c>
       <c r="N6">
-        <v>1.316545756</v>
+        <v>1.313182195</v>
       </c>
       <c r="O6">
-        <v>0.1974818634</v>
+        <v>0.19697732925</v>
       </c>
       <c r="P6">
-        <v>1.1190638926</v>
+        <v>1.11620486575</v>
       </c>
       <c r="Q6">
-        <v>1.2790638926</v>
+        <v>1.27620486575</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1072646076159534</v>
+        <v>0.107817873701663</v>
       </c>
       <c r="T6">
-        <v>0.8010898851298437</v>
+        <v>0.8083007969413482</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>98.85356620557796</v>
+        <v>79.08285296446236</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1045647300165798</v>
+        <v>0.1044452367218445</v>
       </c>
       <c r="C7">
-        <v>6.520194890296519</v>
+        <v>6.461663324825536</v>
       </c>
       <c r="D7">
-        <v>6.458544890296519</v>
+        <v>6.466883324825536</v>
       </c>
       <c r="E7">
-        <v>-0.47265</v>
+        <v>-0.40578</v>
       </c>
       <c r="F7">
-        <v>0.33435</v>
+        <v>0.40122</v>
       </c>
       <c r="G7">
         <v>0.396</v>
@@ -1861,28 +1861,28 @@
         <v>1.33</v>
       </c>
       <c r="M7">
-        <v>0.016817805</v>
+        <v>0.020181366</v>
       </c>
       <c r="N7">
-        <v>1.313182195</v>
+        <v>1.309818634</v>
       </c>
       <c r="O7">
-        <v>0.19697732925</v>
+        <v>0.1964727951</v>
       </c>
       <c r="P7">
-        <v>1.11620486575</v>
+        <v>1.1133458389</v>
       </c>
       <c r="Q7">
-        <v>1.27620486575</v>
+        <v>1.2733458389</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.107817873701663</v>
+        <v>0.1083829114062175</v>
       </c>
       <c r="T7">
-        <v>0.8083007969413482</v>
+        <v>0.8156651324084165</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>79.08285296446236</v>
+        <v>65.9023774703853</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1044452367218444</v>
+        <v>0.1043257434271091</v>
       </c>
       <c r="C8">
-        <v>6.461663324825538</v>
+        <v>6.403153318196392</v>
       </c>
       <c r="D8">
-        <v>6.466883324825538</v>
+        <v>6.475243318196392</v>
       </c>
       <c r="E8">
-        <v>-0.40578</v>
+        <v>-0.3389100000000001</v>
       </c>
       <c r="F8">
-        <v>0.40122</v>
+        <v>0.46809</v>
       </c>
       <c r="G8">
         <v>0.396</v>
@@ -1943,28 +1943,28 @@
         <v>1.33</v>
       </c>
       <c r="M8">
-        <v>0.020181366</v>
+        <v>0.023544927</v>
       </c>
       <c r="N8">
-        <v>1.309818634</v>
+        <v>1.306455073</v>
       </c>
       <c r="O8">
-        <v>0.1964727951</v>
+        <v>0.19596826095</v>
       </c>
       <c r="P8">
-        <v>1.1133458389</v>
+        <v>1.11048681205</v>
       </c>
       <c r="Q8">
-        <v>1.2733458389</v>
+        <v>1.27048681205</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1083829114062175</v>
+        <v>0.1089601004592571</v>
       </c>
       <c r="T8">
-        <v>0.8156651324084165</v>
+        <v>0.8231878406812284</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>65.9023774703853</v>
+        <v>56.48775211747312</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1043257434271091</v>
+        <v>0.1042062501323737</v>
       </c>
       <c r="C9">
-        <v>6.403153318196392</v>
+        <v>6.344664954127186</v>
       </c>
       <c r="D9">
-        <v>6.475243318196393</v>
+        <v>6.483624954127186</v>
       </c>
       <c r="E9">
-        <v>-0.33891</v>
+        <v>-0.2720400000000001</v>
       </c>
       <c r="F9">
-        <v>0.4680900000000001</v>
+        <v>0.53496</v>
       </c>
       <c r="G9">
         <v>0.396</v>
@@ -2025,28 +2025,28 @@
         <v>1.33</v>
       </c>
       <c r="M9">
-        <v>0.023544927</v>
+        <v>0.026908488</v>
       </c>
       <c r="N9">
-        <v>1.306455073</v>
+        <v>1.303091512</v>
       </c>
       <c r="O9">
-        <v>0.19596826095</v>
+        <v>0.1954637268</v>
       </c>
       <c r="P9">
-        <v>1.11048681205</v>
+        <v>1.1076277852</v>
       </c>
       <c r="Q9">
-        <v>1.27048681205</v>
+        <v>1.2676277852</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1089601004592571</v>
+        <v>0.1095498371004062</v>
       </c>
       <c r="T9">
-        <v>0.8231878406812284</v>
+        <v>0.8308740860904057</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>56.48775211747311</v>
+        <v>49.42678310278899</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1042062501323737</v>
+        <v>0.1040867568376383</v>
       </c>
       <c r="C10">
-        <v>6.344664954127186</v>
+        <v>6.286198316770049</v>
       </c>
       <c r="D10">
-        <v>6.483624954127186</v>
+        <v>6.492028316770049</v>
       </c>
       <c r="E10">
-        <v>-0.2720400000000001</v>
+        <v>-0.2051700000000001</v>
       </c>
       <c r="F10">
-        <v>0.53496</v>
+        <v>0.60183</v>
       </c>
       <c r="G10">
         <v>0.396</v>
@@ -2107,28 +2107,28 @@
         <v>1.33</v>
       </c>
       <c r="M10">
-        <v>0.026908488</v>
+        <v>0.030272049</v>
       </c>
       <c r="N10">
-        <v>1.303091512</v>
+        <v>1.299727951</v>
       </c>
       <c r="O10">
-        <v>0.1954637268</v>
+        <v>0.19495919265</v>
       </c>
       <c r="P10">
-        <v>1.1076277852</v>
+        <v>1.10476875835</v>
       </c>
       <c r="Q10">
-        <v>1.2676277852</v>
+        <v>1.26476875835</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1095498371004062</v>
+        <v>0.1101525349864157</v>
       </c>
       <c r="T10">
-        <v>0.8308740860904057</v>
+        <v>0.8387292599701143</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>49.42678310278899</v>
+        <v>43.93491831359021</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1040867568376383</v>
+        <v>0.1039672635429029</v>
       </c>
       <c r="C11">
-        <v>6.286198316770049</v>
+        <v>6.227753490713947</v>
       </c>
       <c r="D11">
-        <v>6.492028316770049</v>
+        <v>6.500453490713947</v>
       </c>
       <c r="E11">
-        <v>-0.2051700000000001</v>
+        <v>-0.1383000000000001</v>
       </c>
       <c r="F11">
-        <v>0.60183</v>
+        <v>0.6687</v>
       </c>
       <c r="G11">
         <v>0.396</v>
@@ -2189,28 +2189,28 @@
         <v>1.33</v>
       </c>
       <c r="M11">
-        <v>0.030272049</v>
+        <v>0.03363561</v>
       </c>
       <c r="N11">
-        <v>1.299727951</v>
+        <v>1.29636439</v>
       </c>
       <c r="O11">
-        <v>0.19495919265</v>
+        <v>0.1944546585</v>
       </c>
       <c r="P11">
-        <v>1.10476875835</v>
+        <v>1.1019097315</v>
       </c>
       <c r="Q11">
-        <v>1.26476875835</v>
+        <v>1.2619097315</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1101525349864157</v>
+        <v>0.110768626158781</v>
       </c>
       <c r="T11">
-        <v>0.8387292599701143</v>
+        <v>0.8467589932693721</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>43.93491831359021</v>
+        <v>39.54142648223119</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1039672635429029</v>
+        <v>0.1038477702481675</v>
       </c>
       <c r="C12">
-        <v>6.227753490713947</v>
+        <v>6.169330560987533</v>
       </c>
       <c r="D12">
-        <v>6.500453490713947</v>
+        <v>6.508900560987533</v>
       </c>
       <c r="E12">
-        <v>-0.1383</v>
+        <v>-0.07142999999999999</v>
       </c>
       <c r="F12">
-        <v>0.6687000000000001</v>
+        <v>0.7355700000000001</v>
       </c>
       <c r="G12">
         <v>0.396</v>
@@ -2271,28 +2271,28 @@
         <v>1.33</v>
       </c>
       <c r="M12">
-        <v>0.03363561</v>
+        <v>0.036999171</v>
       </c>
       <c r="N12">
-        <v>1.29636439</v>
+        <v>1.293000829</v>
       </c>
       <c r="O12">
-        <v>0.1944546585</v>
+        <v>0.19395012435</v>
       </c>
       <c r="P12">
-        <v>1.1019097315</v>
+        <v>1.09905070465</v>
       </c>
       <c r="Q12">
-        <v>1.2619097315</v>
+        <v>1.25905070465</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.110768626158781</v>
+        <v>0.1113985620765927</v>
       </c>
       <c r="T12">
-        <v>0.8467589932693721</v>
+        <v>0.8549691700135569</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>39.54142648223118</v>
+        <v>35.94675134748289</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1038477702481675</v>
+        <v>0.1037282769534321</v>
       </c>
       <c r="C13">
-        <v>6.169330560987533</v>
+        <v>6.110929613061993</v>
       </c>
       <c r="D13">
-        <v>6.508900560987533</v>
+        <v>6.517369613061993</v>
       </c>
       <c r="E13">
-        <v>-0.07142999999999999</v>
+        <v>-0.004560000000000008</v>
       </c>
       <c r="F13">
-        <v>0.7355700000000001</v>
+        <v>0.80244</v>
       </c>
       <c r="G13">
         <v>0.396</v>
@@ -2353,28 +2353,28 @@
         <v>1.33</v>
       </c>
       <c r="M13">
-        <v>0.036999171</v>
+        <v>0.040362732</v>
       </c>
       <c r="N13">
-        <v>1.293000829</v>
+        <v>1.289637268</v>
       </c>
       <c r="O13">
-        <v>0.19395012435</v>
+        <v>0.1934455902</v>
       </c>
       <c r="P13">
-        <v>1.09905070465</v>
+        <v>1.0961916778</v>
       </c>
       <c r="Q13">
-        <v>1.25905070465</v>
+        <v>1.2561916778</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1113985620765927</v>
+        <v>0.1120428147198093</v>
       </c>
       <c r="T13">
-        <v>0.8549691700135569</v>
+        <v>0.863365941683746</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>35.94675134748289</v>
+        <v>32.95118873519266</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1037282769534321</v>
+        <v>0.1036087836586967</v>
       </c>
       <c r="C14">
-        <v>6.110929613061993</v>
+        <v>6.052550732853941</v>
       </c>
       <c r="D14">
-        <v>6.517369613061993</v>
+        <v>6.525860732853941</v>
       </c>
       <c r="E14">
-        <v>-0.004560000000000008</v>
+        <v>0.06230999999999998</v>
       </c>
       <c r="F14">
-        <v>0.80244</v>
+        <v>0.86931</v>
       </c>
       <c r="G14">
         <v>0.396</v>
@@ -2435,28 +2435,28 @@
         <v>1.33</v>
       </c>
       <c r="M14">
-        <v>0.040362732</v>
+        <v>0.043726293</v>
       </c>
       <c r="N14">
-        <v>1.289637268</v>
+        <v>1.286273707</v>
       </c>
       <c r="O14">
-        <v>0.1934455902</v>
+        <v>0.19294105605</v>
       </c>
       <c r="P14">
-        <v>1.0961916778</v>
+        <v>1.09333265095</v>
       </c>
       <c r="Q14">
-        <v>1.2561916778</v>
+        <v>1.25333265095</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1120428147198093</v>
+        <v>0.112701877768617</v>
       </c>
       <c r="T14">
-        <v>0.863365941683746</v>
+        <v>0.8719557425877325</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>32.95118873519266</v>
+        <v>30.41648190940861</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1036087836586967</v>
+        <v>0.1034892903639614</v>
       </c>
       <c r="C15">
-        <v>6.052550732853941</v>
+        <v>5.994194006728313</v>
       </c>
       <c r="D15">
-        <v>6.525860732853941</v>
+        <v>6.534374006728314</v>
       </c>
       <c r="E15">
-        <v>0.06230999999999998</v>
+        <v>0.1291800000000001</v>
       </c>
       <c r="F15">
-        <v>0.86931</v>
+        <v>0.9361800000000001</v>
       </c>
       <c r="G15">
         <v>0.396</v>
@@ -2517,28 +2517,28 @@
         <v>1.33</v>
       </c>
       <c r="M15">
-        <v>0.043726293</v>
+        <v>0.047089854</v>
       </c>
       <c r="N15">
-        <v>1.286273707</v>
+        <v>1.282910146</v>
       </c>
       <c r="O15">
-        <v>0.19294105605</v>
+        <v>0.1924365219</v>
       </c>
       <c r="P15">
-        <v>1.09333265095</v>
+        <v>1.0904736241</v>
       </c>
       <c r="Q15">
-        <v>1.25333265095</v>
+        <v>1.2504736241</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.112701877768617</v>
+        <v>0.1133762678650714</v>
       </c>
       <c r="T15">
-        <v>0.8719557425877325</v>
+        <v>0.8807453063034395</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>30.41648190940861</v>
+        <v>28.24387605873656</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1034892903639614</v>
+        <v>0.103369797069226</v>
       </c>
       <c r="C16">
-        <v>5.994194006728313</v>
+        <v>5.935859521501309</v>
       </c>
       <c r="D16">
-        <v>6.534374006728314</v>
+        <v>6.54290952150131</v>
       </c>
       <c r="E16">
-        <v>0.1291800000000001</v>
+        <v>0.1960500000000002</v>
       </c>
       <c r="F16">
-        <v>0.9361800000000001</v>
+        <v>1.00305</v>
       </c>
       <c r="G16">
         <v>0.396</v>
@@ -2599,28 +2599,28 @@
         <v>1.33</v>
       </c>
       <c r="M16">
-        <v>0.047089854</v>
+        <v>0.05045341500000001</v>
       </c>
       <c r="N16">
-        <v>1.282910146</v>
+        <v>1.279546585</v>
       </c>
       <c r="O16">
-        <v>0.1924365219</v>
+        <v>0.19193198775</v>
       </c>
       <c r="P16">
-        <v>1.0904736241</v>
+        <v>1.08761459725</v>
       </c>
       <c r="Q16">
-        <v>1.2504736241</v>
+        <v>1.24761459725</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1133762678650714</v>
+        <v>0.1140665259637953</v>
       </c>
       <c r="T16">
-        <v>0.8807453063034395</v>
+        <v>0.8897416832830457</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>28.24387605873656</v>
+        <v>26.36095098815412</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.103369797069226</v>
+        <v>0.1032503037744906</v>
       </c>
       <c r="C17">
-        <v>5.935859521501309</v>
+        <v>5.877547364443331</v>
       </c>
       <c r="D17">
-        <v>6.54290952150131</v>
+        <v>6.551467364443331</v>
       </c>
       <c r="E17">
-        <v>0.1960499999999999</v>
+        <v>0.2629199999999999</v>
       </c>
       <c r="F17">
-        <v>1.00305</v>
+        <v>1.06992</v>
       </c>
       <c r="G17">
         <v>0.396</v>
@@ -2681,28 +2681,28 @@
         <v>1.33</v>
       </c>
       <c r="M17">
-        <v>0.05045341499999999</v>
+        <v>0.053816976</v>
       </c>
       <c r="N17">
-        <v>1.279546585</v>
+        <v>1.276183024</v>
       </c>
       <c r="O17">
-        <v>0.19193198775</v>
+        <v>0.1914274536</v>
       </c>
       <c r="P17">
-        <v>1.08761459725</v>
+        <v>1.0847555704</v>
       </c>
       <c r="Q17">
-        <v>1.24761459725</v>
+        <v>1.2447555704</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1140665259637953</v>
+        <v>0.1147732187791555</v>
       </c>
       <c r="T17">
-        <v>0.8897416832830457</v>
+        <v>0.8989522597145473</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>26.36095098815413</v>
+        <v>24.71339155139449</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1032503037744906</v>
+        <v>0.1031308104797552</v>
       </c>
       <c r="C18">
-        <v>5.877547364443331</v>
+        <v>5.819257623281962</v>
       </c>
       <c r="D18">
-        <v>6.551467364443331</v>
+        <v>6.560047623281962</v>
       </c>
       <c r="E18">
-        <v>0.2629199999999999</v>
+        <v>0.3297900000000001</v>
       </c>
       <c r="F18">
-        <v>1.06992</v>
+        <v>1.13679</v>
       </c>
       <c r="G18">
         <v>0.396</v>
@@ -2763,28 +2763,28 @@
         <v>1.33</v>
       </c>
       <c r="M18">
-        <v>0.053816976</v>
+        <v>0.057180537</v>
       </c>
       <c r="N18">
-        <v>1.276183024</v>
+        <v>1.272819463</v>
       </c>
       <c r="O18">
-        <v>0.1914274536</v>
+        <v>0.19092291945</v>
       </c>
       <c r="P18">
-        <v>1.0847555704</v>
+        <v>1.08189654355</v>
       </c>
       <c r="Q18">
-        <v>1.2447555704</v>
+        <v>1.24189654355</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1147732187791555</v>
+        <v>0.1154969403370545</v>
       </c>
       <c r="T18">
-        <v>0.8989522597145473</v>
+        <v>0.9083847777468078</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>24.71339155139449</v>
+        <v>23.25966263660658</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1031308104797552</v>
+        <v>0.1030113171850198</v>
       </c>
       <c r="C19">
-        <v>5.819257623281962</v>
+        <v>5.760990386204965</v>
       </c>
       <c r="D19">
-        <v>6.560047623281962</v>
+        <v>6.568650386204966</v>
       </c>
       <c r="E19">
-        <v>0.3297900000000001</v>
+        <v>0.3966600000000001</v>
       </c>
       <c r="F19">
-        <v>1.13679</v>
+        <v>1.20366</v>
       </c>
       <c r="G19">
         <v>0.396</v>
@@ -2845,28 +2845,28 @@
         <v>1.33</v>
       </c>
       <c r="M19">
-        <v>0.057180537</v>
+        <v>0.060544098</v>
       </c>
       <c r="N19">
-        <v>1.272819463</v>
+        <v>1.269455902</v>
       </c>
       <c r="O19">
-        <v>0.19092291945</v>
+        <v>0.1904183853</v>
       </c>
       <c r="P19">
-        <v>1.08189654355</v>
+        <v>1.0790375167</v>
       </c>
       <c r="Q19">
-        <v>1.24189654355</v>
+        <v>1.2390375167</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1154969403370545</v>
+        <v>0.1162383136402681</v>
       </c>
       <c r="T19">
-        <v>0.9083847777468078</v>
+        <v>0.9180473571944894</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>23.25966263660658</v>
+        <v>21.9674591567951</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1030113171850198</v>
+        <v>0.1028918238902845</v>
       </c>
       <c r="C20">
-        <v>5.760990386204965</v>
+        <v>5.702745741863309</v>
       </c>
       <c r="D20">
-        <v>6.568650386204966</v>
+        <v>6.577275741863309</v>
       </c>
       <c r="E20">
-        <v>0.3966599999999999</v>
+        <v>0.4635300000000001</v>
       </c>
       <c r="F20">
-        <v>1.20366</v>
+        <v>1.27053</v>
       </c>
       <c r="G20">
         <v>0.396</v>
@@ -2927,28 +2927,28 @@
         <v>1.33</v>
       </c>
       <c r="M20">
-        <v>0.060544098</v>
+        <v>0.06390765900000001</v>
       </c>
       <c r="N20">
-        <v>1.269455902</v>
+        <v>1.266092341</v>
       </c>
       <c r="O20">
-        <v>0.1904183853</v>
+        <v>0.18991385115</v>
       </c>
       <c r="P20">
-        <v>1.0790375167</v>
+        <v>1.07617848985</v>
       </c>
       <c r="Q20">
-        <v>1.2390375167</v>
+        <v>1.23617848985</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1162383136402681</v>
+        <v>0.1169979924571413</v>
       </c>
       <c r="T20">
-        <v>0.9180473571944894</v>
+        <v>0.9279485188507556</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>21.9674591567951</v>
+        <v>20.81127709591115</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1028918238902845</v>
+        <v>0.102772330595549</v>
       </c>
       <c r="C21">
-        <v>5.702745741863309</v>
+        <v>5.644523779374204</v>
       </c>
       <c r="D21">
-        <v>6.577275741863309</v>
+        <v>6.585923779374204</v>
       </c>
       <c r="E21">
-        <v>0.4635300000000001</v>
+        <v>0.5304000000000001</v>
       </c>
       <c r="F21">
-        <v>1.27053</v>
+        <v>1.3374</v>
       </c>
       <c r="G21">
         <v>0.396</v>
@@ -3009,28 +3009,28 @@
         <v>1.33</v>
       </c>
       <c r="M21">
-        <v>0.06390765900000001</v>
+        <v>0.06727122000000001</v>
       </c>
       <c r="N21">
-        <v>1.266092341</v>
+        <v>1.26272878</v>
       </c>
       <c r="O21">
-        <v>0.18991385115</v>
+        <v>0.189409317</v>
       </c>
       <c r="P21">
-        <v>1.07617848985</v>
+        <v>1.073319463</v>
       </c>
       <c r="Q21">
-        <v>1.23617848985</v>
+        <v>1.233319463</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1169979924571413</v>
+        <v>0.1177766632444363</v>
       </c>
       <c r="T21">
-        <v>0.9279485188507556</v>
+        <v>0.9380972095484286</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>20.81127709591115</v>
+        <v>19.77071324111559</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.102772330595549</v>
+        <v>0.1026528373008137</v>
       </c>
       <c r="C22">
-        <v>5.644523779374204</v>
+        <v>5.586324588324172</v>
       </c>
       <c r="D22">
-        <v>6.585923779374204</v>
+        <v>6.594594588324172</v>
       </c>
       <c r="E22">
-        <v>0.5304000000000001</v>
+        <v>0.5972700000000001</v>
       </c>
       <c r="F22">
-        <v>1.3374</v>
+        <v>1.40427</v>
       </c>
       <c r="G22">
         <v>0.396</v>
@@ -3091,28 +3091,28 @@
         <v>1.33</v>
       </c>
       <c r="M22">
-        <v>0.06727122000000001</v>
+        <v>0.07063478100000001</v>
       </c>
       <c r="N22">
-        <v>1.26272878</v>
+        <v>1.259365219</v>
       </c>
       <c r="O22">
-        <v>0.189409317</v>
+        <v>0.18890478285</v>
       </c>
       <c r="P22">
-        <v>1.073319463</v>
+        <v>1.07046043615</v>
       </c>
       <c r="Q22">
-        <v>1.233319463</v>
+        <v>1.23046043615</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1177766632444363</v>
+        <v>0.1185750472162198</v>
       </c>
       <c r="T22">
-        <v>0.9380972095484286</v>
+        <v>0.9485028291245238</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>19.77071324111559</v>
+        <v>18.82925070582437</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1026528373008137</v>
+        <v>0.1025333440060783</v>
       </c>
       <c r="C23">
-        <v>5.586324588324173</v>
+        <v>5.528148258772151</v>
       </c>
       <c r="D23">
-        <v>6.594594588324172</v>
+        <v>6.603288258772151</v>
       </c>
       <c r="E23">
-        <v>0.5972699999999999</v>
+        <v>0.6641400000000001</v>
       </c>
       <c r="F23">
-        <v>1.40427</v>
+        <v>1.47114</v>
       </c>
       <c r="G23">
         <v>0.396</v>
@@ -3173,28 +3173,28 @@
         <v>1.33</v>
       </c>
       <c r="M23">
-        <v>0.07063478099999999</v>
+        <v>0.07399834200000001</v>
       </c>
       <c r="N23">
-        <v>1.259365219</v>
+        <v>1.256001658</v>
       </c>
       <c r="O23">
-        <v>0.18890478285</v>
+        <v>0.1884002487</v>
       </c>
       <c r="P23">
-        <v>1.07046043615</v>
+        <v>1.0676014093</v>
       </c>
       <c r="Q23">
-        <v>1.23046043615</v>
+        <v>1.2276014093</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1185750472162198</v>
+        <v>0.1193939025718952</v>
       </c>
       <c r="T23">
-        <v>0.9485028291245235</v>
+        <v>0.9591752594589802</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>18.82925070582437</v>
+        <v>17.97337567374144</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1025333440060783</v>
+        <v>0.1024138507113429</v>
       </c>
       <c r="C24">
-        <v>5.528148258772151</v>
+        <v>5.469994881252602</v>
       </c>
       <c r="D24">
-        <v>6.603288258772151</v>
+        <v>6.612004881252602</v>
       </c>
       <c r="E24">
-        <v>0.6641400000000001</v>
+        <v>0.73101</v>
       </c>
       <c r="F24">
-        <v>1.47114</v>
+        <v>1.53801</v>
       </c>
       <c r="G24">
         <v>0.396</v>
@@ -3255,28 +3255,28 @@
         <v>1.33</v>
       </c>
       <c r="M24">
-        <v>0.07399834200000001</v>
+        <v>0.077361903</v>
       </c>
       <c r="N24">
-        <v>1.256001658</v>
+        <v>1.252638097</v>
       </c>
       <c r="O24">
-        <v>0.1884002487</v>
+        <v>0.18789571455</v>
       </c>
       <c r="P24">
-        <v>1.0676014093</v>
+        <v>1.06474238245</v>
       </c>
       <c r="Q24">
-        <v>1.2276014093</v>
+        <v>1.22474238245</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1193939025718952</v>
+        <v>0.1202340268978479</v>
       </c>
       <c r="T24">
-        <v>0.9591752594589802</v>
+        <v>0.9701248957761498</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>17.97337567374144</v>
+        <v>17.19192455749182</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1024138507113429</v>
+        <v>0.1022943574166075</v>
       </c>
       <c r="C25">
-        <v>5.469994881252602</v>
+        <v>5.411864546778652</v>
       </c>
       <c r="D25">
-        <v>6.612004881252602</v>
+        <v>6.620744546778653</v>
       </c>
       <c r="E25">
-        <v>0.73101</v>
+        <v>0.79788</v>
       </c>
       <c r="F25">
-        <v>1.53801</v>
+        <v>1.60488</v>
       </c>
       <c r="G25">
         <v>0.396</v>
@@ -3337,28 +3337,28 @@
         <v>1.33</v>
       </c>
       <c r="M25">
-        <v>0.077361903</v>
+        <v>0.080725464</v>
       </c>
       <c r="N25">
-        <v>1.252638097</v>
+        <v>1.249274536</v>
       </c>
       <c r="O25">
-        <v>0.18789571455</v>
+        <v>0.1873911804</v>
       </c>
       <c r="P25">
-        <v>1.06474238245</v>
+        <v>1.0618833556</v>
       </c>
       <c r="Q25">
-        <v>1.22474238245</v>
+        <v>1.2218833556</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1202340268978479</v>
+        <v>0.1210962597586941</v>
       </c>
       <c r="T25">
-        <v>0.9701248957761498</v>
+        <v>0.9813626804174554</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.19192455749182</v>
+        <v>16.47559436759633</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1022943574166075</v>
+        <v>0.1021748641218721</v>
       </c>
       <c r="C26">
-        <v>5.411864546778652</v>
+        <v>5.353757346845272</v>
       </c>
       <c r="D26">
-        <v>6.620744546778653</v>
+        <v>6.629507346845273</v>
       </c>
       <c r="E26">
-        <v>0.79788</v>
+        <v>0.86475</v>
       </c>
       <c r="F26">
-        <v>1.60488</v>
+        <v>1.67175</v>
       </c>
       <c r="G26">
         <v>0.396</v>
@@ -3419,28 +3419,28 @@
         <v>1.33</v>
       </c>
       <c r="M26">
-        <v>0.080725464</v>
+        <v>0.084089025</v>
       </c>
       <c r="N26">
-        <v>1.249274536</v>
+        <v>1.245910975</v>
       </c>
       <c r="O26">
-        <v>0.1873911804</v>
+        <v>0.18688664625</v>
       </c>
       <c r="P26">
-        <v>1.0618833556</v>
+        <v>1.05902432875</v>
       </c>
       <c r="Q26">
-        <v>1.2218833556</v>
+        <v>1.21902432875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1210962597586941</v>
+        <v>0.1219814854958295</v>
       </c>
       <c r="T26">
-        <v>0.9813626804174554</v>
+        <v>0.9929001393158625</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.47559436759633</v>
+        <v>15.81657059289248</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1021748641218721</v>
+        <v>0.1020553708271367</v>
       </c>
       <c r="C27">
-        <v>5.353757346845272</v>
+        <v>5.295673373432456</v>
       </c>
       <c r="D27">
-        <v>6.629507346845273</v>
+        <v>6.638293373432457</v>
       </c>
       <c r="E27">
-        <v>0.86475</v>
+        <v>0.93162</v>
       </c>
       <c r="F27">
-        <v>1.67175</v>
+        <v>1.73862</v>
       </c>
       <c r="G27">
         <v>0.396</v>
@@ -3501,28 +3501,28 @@
         <v>1.33</v>
       </c>
       <c r="M27">
-        <v>0.084089025</v>
+        <v>0.087452586</v>
       </c>
       <c r="N27">
-        <v>1.245910975</v>
+        <v>1.242547414</v>
       </c>
       <c r="O27">
-        <v>0.18688664625</v>
+        <v>0.1863821121</v>
       </c>
       <c r="P27">
-        <v>1.05902432875</v>
+        <v>1.0561653019</v>
       </c>
       <c r="Q27">
-        <v>1.21902432875</v>
+        <v>1.2161653019</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1219814854958295</v>
+        <v>0.1228906362528875</v>
       </c>
       <c r="T27">
-        <v>0.9929001393158625</v>
+        <v>1.00474942142774</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.81657059289248</v>
+        <v>15.2082409547043</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1020553708271367</v>
+        <v>0.1019358775324014</v>
       </c>
       <c r="C28">
-        <v>5.295673373432456</v>
+        <v>5.23761271900845</v>
       </c>
       <c r="D28">
-        <v>6.638293373432457</v>
+        <v>6.64710271900845</v>
       </c>
       <c r="E28">
-        <v>0.93162</v>
+        <v>0.9984900000000002</v>
       </c>
       <c r="F28">
-        <v>1.73862</v>
+        <v>1.80549</v>
       </c>
       <c r="G28">
         <v>0.396</v>
@@ -3583,28 +3583,28 @@
         <v>1.33</v>
       </c>
       <c r="M28">
-        <v>0.087452586</v>
+        <v>0.09081614700000001</v>
       </c>
       <c r="N28">
-        <v>1.242547414</v>
+        <v>1.239183853</v>
       </c>
       <c r="O28">
-        <v>0.1863821121</v>
+        <v>0.18587757795</v>
       </c>
       <c r="P28">
-        <v>1.0561653019</v>
+        <v>1.05330627505</v>
       </c>
       <c r="Q28">
-        <v>1.2161653019</v>
+        <v>1.21330627505</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1228906362528875</v>
+        <v>0.1238246952498649</v>
       </c>
       <c r="T28">
-        <v>1.00474942142774</v>
+        <v>1.016923341405697</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.2082409547043</v>
+        <v>14.64497277119673</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1019358775324014</v>
+        <v>0.101816384237666</v>
       </c>
       <c r="C29">
-        <v>5.23761271900845</v>
+        <v>5.17957547653299</v>
       </c>
       <c r="D29">
-        <v>6.64710271900845</v>
+        <v>6.65593547653299</v>
       </c>
       <c r="E29">
-        <v>0.9984900000000002</v>
+        <v>1.06536</v>
       </c>
       <c r="F29">
-        <v>1.80549</v>
+        <v>1.87236</v>
       </c>
       <c r="G29">
         <v>0.396</v>
@@ -3665,28 +3665,28 @@
         <v>1.33</v>
       </c>
       <c r="M29">
-        <v>0.09081614700000001</v>
+        <v>0.094179708</v>
       </c>
       <c r="N29">
-        <v>1.239183853</v>
+        <v>1.235820292</v>
       </c>
       <c r="O29">
-        <v>0.18587757795</v>
+        <v>0.1853730438</v>
       </c>
       <c r="P29">
-        <v>1.05330627505</v>
+        <v>1.0504472482</v>
       </c>
       <c r="Q29">
-        <v>1.21330627505</v>
+        <v>1.2104472482</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1238246952498649</v>
+        <v>0.1247847003300916</v>
       </c>
       <c r="T29">
-        <v>1.016923341405697</v>
+        <v>1.029435425827485</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.64497277119673</v>
+        <v>14.12193802936828</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.101816384237666</v>
+        <v>0.1016968909429306</v>
       </c>
       <c r="C30">
-        <v>5.17957547653299</v>
+        <v>5.121561739460579</v>
       </c>
       <c r="D30">
-        <v>6.65593547653299</v>
+        <v>6.664791739460579</v>
       </c>
       <c r="E30">
-        <v>1.06536</v>
+        <v>1.13223</v>
       </c>
       <c r="F30">
-        <v>1.87236</v>
+        <v>1.93923</v>
       </c>
       <c r="G30">
         <v>0.396</v>
@@ -3747,28 +3747,28 @@
         <v>1.33</v>
       </c>
       <c r="M30">
-        <v>0.094179708</v>
+        <v>0.097543269</v>
       </c>
       <c r="N30">
-        <v>1.235820292</v>
+        <v>1.232456731</v>
       </c>
       <c r="O30">
-        <v>0.1853730438</v>
+        <v>0.18486850965</v>
       </c>
       <c r="P30">
-        <v>1.0504472482</v>
+        <v>1.04758822135</v>
       </c>
       <c r="Q30">
-        <v>1.2104472482</v>
+        <v>1.20758822135</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1247847003300916</v>
+        <v>0.1257717478069445</v>
       </c>
       <c r="T30">
-        <v>1.029435425827485</v>
+        <v>1.042299963331578</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.12193802936828</v>
+        <v>13.63497464904524</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1016968909429306</v>
+        <v>0.1015773976481952</v>
       </c>
       <c r="C31">
-        <v>5.121561739460579</v>
+        <v>5.063571601743769</v>
       </c>
       <c r="D31">
-        <v>6.664791739460579</v>
+        <v>6.673671601743769</v>
       </c>
       <c r="E31">
-        <v>1.13223</v>
+        <v>1.1991</v>
       </c>
       <c r="F31">
-        <v>1.93923</v>
+        <v>2.0061</v>
       </c>
       <c r="G31">
         <v>0.396</v>
@@ -3829,28 +3829,28 @@
         <v>1.33</v>
       </c>
       <c r="M31">
-        <v>0.097543269</v>
+        <v>0.10090683</v>
       </c>
       <c r="N31">
-        <v>1.232456731</v>
+        <v>1.22909317</v>
       </c>
       <c r="O31">
-        <v>0.18486850965</v>
+        <v>0.1843639755</v>
       </c>
       <c r="P31">
-        <v>1.04758822135</v>
+        <v>1.0447291945</v>
       </c>
       <c r="Q31">
-        <v>1.20758822135</v>
+        <v>1.2047291945</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1257717478069445</v>
+        <v>0.1267869966402789</v>
       </c>
       <c r="T31">
-        <v>1.042299963331578</v>
+        <v>1.055532059050073</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.63497464904524</v>
+        <v>13.18047549407706</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1015773976481952</v>
+        <v>0.1018531543534598</v>
       </c>
       <c r="C32">
-        <v>5.063571601743769</v>
+        <v>4.97624498776517</v>
       </c>
       <c r="D32">
-        <v>6.673671601743769</v>
+        <v>6.65321498776517</v>
       </c>
       <c r="E32">
-        <v>1.1991</v>
+        <v>1.26597</v>
       </c>
       <c r="F32">
-        <v>2.0061</v>
+        <v>2.07297</v>
       </c>
       <c r="G32">
         <v>0.396</v>
@@ -3911,45 +3911,45 @@
         <v>1.33</v>
       </c>
       <c r="M32">
-        <v>0.10090683</v>
+        <v>0.107379846</v>
       </c>
       <c r="N32">
-        <v>1.22909317</v>
+        <v>1.222620154</v>
       </c>
       <c r="O32">
-        <v>0.1843639755</v>
+        <v>0.1833930231</v>
       </c>
       <c r="P32">
-        <v>1.0447291945</v>
+        <v>1.0392271309</v>
       </c>
       <c r="Q32">
-        <v>1.2047291945</v>
+        <v>1.1992271309</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1267869966402789</v>
+        <v>0.1278316729760287</v>
       </c>
       <c r="T32">
-        <v>1.055532059050073</v>
+        <v>1.069147693774901</v>
       </c>
       <c r="U32">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V32">
         <v>0.15</v>
       </c>
       <c r="W32">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y32">
-        <v>13.18047549407706</v>
+        <v>12.38593692898386</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1018531543534598</v>
+        <v>0.1017464110587244</v>
       </c>
       <c r="C33">
-        <v>4.97624498776517</v>
+        <v>4.917278690764263</v>
       </c>
       <c r="D33">
-        <v>6.65321498776517</v>
+        <v>6.661118690764264</v>
       </c>
       <c r="E33">
-        <v>1.26597</v>
+        <v>1.33284</v>
       </c>
       <c r="F33">
-        <v>2.07297</v>
+        <v>2.13984</v>
       </c>
       <c r="G33">
         <v>0.396</v>
@@ -3993,28 +3993,28 @@
         <v>1.33</v>
       </c>
       <c r="M33">
-        <v>0.107379846</v>
+        <v>0.110843712</v>
       </c>
       <c r="N33">
-        <v>1.222620154</v>
+        <v>1.219156288</v>
       </c>
       <c r="O33">
-        <v>0.1833930231</v>
+        <v>0.1828734432</v>
       </c>
       <c r="P33">
-        <v>1.0392271309</v>
+        <v>1.0362828448</v>
       </c>
       <c r="Q33">
-        <v>1.1992271309</v>
+        <v>1.1962828448</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1278316729760287</v>
+        <v>0.1289070750863595</v>
       </c>
       <c r="T33">
-        <v>1.069147693774901</v>
+        <v>1.083163788344577</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>12.38593692898386</v>
+        <v>11.99887639995312</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1017464110587244</v>
+        <v>0.101639667763989</v>
       </c>
       <c r="C34">
-        <v>4.917278690764263</v>
+        <v>4.858331194544367</v>
       </c>
       <c r="D34">
-        <v>6.661118690764264</v>
+        <v>6.669041194544367</v>
       </c>
       <c r="E34">
-        <v>1.33284</v>
+        <v>1.39971</v>
       </c>
       <c r="F34">
-        <v>2.13984</v>
+        <v>2.20671</v>
       </c>
       <c r="G34">
         <v>0.396</v>
@@ -4075,28 +4075,28 @@
         <v>1.33</v>
       </c>
       <c r="M34">
-        <v>0.110843712</v>
+        <v>0.114307578</v>
       </c>
       <c r="N34">
-        <v>1.219156288</v>
+        <v>1.215692422</v>
       </c>
       <c r="O34">
-        <v>0.1828734432</v>
+        <v>0.1823538633</v>
       </c>
       <c r="P34">
-        <v>1.0362828448</v>
+        <v>1.0333385587</v>
       </c>
       <c r="Q34">
-        <v>1.1962828448</v>
+        <v>1.1933385587</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1289070750863595</v>
+        <v>0.1300145787522225</v>
       </c>
       <c r="T34">
-        <v>1.083163788344577</v>
+        <v>1.097598273796931</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>11.99887639995312</v>
+        <v>11.63527408480302</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.101639667763989</v>
+        <v>0.1015329244692536</v>
       </c>
       <c r="C35">
-        <v>4.858331194544367</v>
+        <v>4.799402566268354</v>
       </c>
       <c r="D35">
-        <v>6.669041194544367</v>
+        <v>6.676982566268354</v>
       </c>
       <c r="E35">
-        <v>1.39971</v>
+        <v>1.46658</v>
       </c>
       <c r="F35">
-        <v>2.20671</v>
+        <v>2.27358</v>
       </c>
       <c r="G35">
         <v>0.396</v>
@@ -4157,28 +4157,28 @@
         <v>1.33</v>
       </c>
       <c r="M35">
-        <v>0.114307578</v>
+        <v>0.117771444</v>
       </c>
       <c r="N35">
-        <v>1.215692422</v>
+        <v>1.212228556</v>
       </c>
       <c r="O35">
-        <v>0.1823538633</v>
+        <v>0.1818342834</v>
       </c>
       <c r="P35">
-        <v>1.0333385587</v>
+        <v>1.0303942726</v>
       </c>
       <c r="Q35">
-        <v>1.1933385587</v>
+        <v>1.1903942726</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1300145787522225</v>
+        <v>0.1311556431352328</v>
       </c>
       <c r="T35">
-        <v>1.097598273796931</v>
+        <v>1.112470167899355</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.63527408480302</v>
+        <v>11.29306014113234</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1015329244692536</v>
+        <v>0.1014261811745183</v>
       </c>
       <c r="C36">
-        <v>4.799402566268354</v>
+        <v>4.740492873419381</v>
       </c>
       <c r="D36">
-        <v>6.676982566268354</v>
+        <v>6.684942873419381</v>
       </c>
       <c r="E36">
-        <v>1.46658</v>
+        <v>1.53345</v>
       </c>
       <c r="F36">
-        <v>2.27358</v>
+        <v>2.34045</v>
       </c>
       <c r="G36">
         <v>0.396</v>
@@ -4239,28 +4239,28 @@
         <v>1.33</v>
       </c>
       <c r="M36">
-        <v>0.117771444</v>
+        <v>0.12123531</v>
       </c>
       <c r="N36">
-        <v>1.212228556</v>
+        <v>1.20876469</v>
       </c>
       <c r="O36">
-        <v>0.1818342834</v>
+        <v>0.1813147035</v>
       </c>
       <c r="P36">
-        <v>1.0303942726</v>
+        <v>1.0274499865</v>
       </c>
       <c r="Q36">
-        <v>1.1903942726</v>
+        <v>1.1874499865</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1311556431352328</v>
+        <v>0.1323318171915666</v>
       </c>
       <c r="T36">
-        <v>1.112470167899355</v>
+        <v>1.127799658743392</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.29306014113234</v>
+        <v>10.97040127995713</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1014261811745183</v>
+        <v>0.1013194378797829</v>
       </c>
       <c r="C37">
-        <v>4.740492873419381</v>
+        <v>4.681602183802808</v>
       </c>
       <c r="D37">
-        <v>6.684942873419381</v>
+        <v>6.692922183802809</v>
       </c>
       <c r="E37">
-        <v>1.53345</v>
+        <v>1.60032</v>
       </c>
       <c r="F37">
-        <v>2.34045</v>
+        <v>2.40732</v>
       </c>
       <c r="G37">
         <v>0.396</v>
@@ -4321,28 +4321,28 @@
         <v>1.33</v>
       </c>
       <c r="M37">
-        <v>0.12123531</v>
+        <v>0.124699176</v>
       </c>
       <c r="N37">
-        <v>1.20876469</v>
+        <v>1.205300824</v>
       </c>
       <c r="O37">
-        <v>0.1813147035</v>
+        <v>0.1807951236</v>
       </c>
       <c r="P37">
-        <v>1.0274499865</v>
+        <v>1.0245057004</v>
       </c>
       <c r="Q37">
-        <v>1.1874499865</v>
+        <v>1.1845057004</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1323318171915666</v>
+        <v>0.1335447466871608</v>
       </c>
       <c r="T37">
-        <v>1.127799658743392</v>
+        <v>1.143608196176306</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>10.97040127995713</v>
+        <v>10.66566791106944</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1013194378797829</v>
+        <v>0.1012126945850475</v>
       </c>
       <c r="C38">
-        <v>4.681602183802809</v>
+        <v>4.62273056554812</v>
       </c>
       <c r="D38">
-        <v>6.692922183802809</v>
+        <v>6.70092056554812</v>
       </c>
       <c r="E38">
-        <v>1.60032</v>
+        <v>1.66719</v>
       </c>
       <c r="F38">
-        <v>2.40732</v>
+        <v>2.47419</v>
       </c>
       <c r="G38">
         <v>0.396</v>
@@ -4403,28 +4403,28 @@
         <v>1.33</v>
       </c>
       <c r="M38">
-        <v>0.124699176</v>
+        <v>0.128163042</v>
       </c>
       <c r="N38">
-        <v>1.205300824</v>
+        <v>1.201836958</v>
       </c>
       <c r="O38">
-        <v>0.1807951236</v>
+        <v>0.1802755437</v>
       </c>
       <c r="P38">
-        <v>1.0245057004</v>
+        <v>1.0215614143</v>
       </c>
       <c r="Q38">
-        <v>1.1845057004</v>
+        <v>1.1815614143</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1335447466871608</v>
+        <v>0.1347961818810278</v>
       </c>
       <c r="T38">
-        <v>1.143608196176306</v>
+        <v>1.159918591940423</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.66566791106944</v>
+        <v>10.37740661617567</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1012126945850475</v>
+        <v>0.1011059512903121</v>
       </c>
       <c r="C39">
-        <v>4.62273056554812</v>
+        <v>4.563878087110858</v>
       </c>
       <c r="D39">
-        <v>6.70092056554812</v>
+        <v>6.708938087110859</v>
       </c>
       <c r="E39">
-        <v>1.66719</v>
+        <v>1.73406</v>
       </c>
       <c r="F39">
-        <v>2.47419</v>
+        <v>2.54106</v>
       </c>
       <c r="G39">
         <v>0.396</v>
@@ -4485,28 +4485,28 @@
         <v>1.33</v>
       </c>
       <c r="M39">
-        <v>0.128163042</v>
+        <v>0.131626908</v>
       </c>
       <c r="N39">
-        <v>1.201836958</v>
+        <v>1.198373092</v>
       </c>
       <c r="O39">
-        <v>0.1802755437</v>
+        <v>0.1797559638</v>
       </c>
       <c r="P39">
-        <v>1.0215614143</v>
+        <v>1.0186171282</v>
       </c>
       <c r="Q39">
-        <v>1.1815614143</v>
+        <v>1.1786171282</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1347961818810278</v>
+        <v>0.1360879859521163</v>
       </c>
       <c r="T39">
-        <v>1.159918591940423</v>
+        <v>1.176755129503383</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.37740661617567</v>
+        <v>10.10431696838157</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1011059512903121</v>
+        <v>0.1009992079955767</v>
       </c>
       <c r="C40">
-        <v>4.563878087110858</v>
+        <v>4.505044817274586</v>
       </c>
       <c r="D40">
-        <v>6.708938087110859</v>
+        <v>6.716974817274586</v>
       </c>
       <c r="E40">
-        <v>1.73406</v>
+        <v>1.80093</v>
       </c>
       <c r="F40">
-        <v>2.54106</v>
+        <v>2.60793</v>
       </c>
       <c r="G40">
         <v>0.396</v>
@@ -4567,28 +4567,28 @@
         <v>1.33</v>
       </c>
       <c r="M40">
-        <v>0.131626908</v>
+        <v>0.135090774</v>
       </c>
       <c r="N40">
-        <v>1.198373092</v>
+        <v>1.194909226</v>
       </c>
       <c r="O40">
-        <v>0.1797559638</v>
+        <v>0.1792363839</v>
       </c>
       <c r="P40">
-        <v>1.0186171282</v>
+        <v>1.0156728421</v>
       </c>
       <c r="Q40">
-        <v>1.1786171282</v>
+        <v>1.1756728421</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1360879859521163</v>
+        <v>0.1374221442550438</v>
       </c>
       <c r="T40">
-        <v>1.176755129503383</v>
+        <v>1.194143684691358</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.10431696838157</v>
+        <v>9.845231917910249</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1009992079955767</v>
+        <v>0.1014704647008414</v>
       </c>
       <c r="C41">
-        <v>4.505044817274586</v>
+        <v>4.402838157525953</v>
       </c>
       <c r="D41">
-        <v>6.716974817274586</v>
+        <v>6.681638157525954</v>
       </c>
       <c r="E41">
-        <v>1.80093</v>
+        <v>1.8678</v>
       </c>
       <c r="F41">
-        <v>2.60793</v>
+        <v>2.6748</v>
       </c>
       <c r="G41">
         <v>0.396</v>
@@ -4649,45 +4649,45 @@
         <v>1.33</v>
       </c>
       <c r="M41">
-        <v>0.135090774</v>
+        <v>0.1431018</v>
       </c>
       <c r="N41">
-        <v>1.194909226</v>
+        <v>1.1868982</v>
       </c>
       <c r="O41">
-        <v>0.1792363839</v>
+        <v>0.17803473</v>
       </c>
       <c r="P41">
-        <v>1.0156728421</v>
+        <v>1.00886347</v>
       </c>
       <c r="Q41">
-        <v>1.1756728421</v>
+        <v>1.16886347</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1374221442550438</v>
+        <v>0.1388007745014023</v>
       </c>
       <c r="T41">
-        <v>1.194143684691358</v>
+        <v>1.212111858385599</v>
       </c>
       <c r="U41">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V41">
         <v>0.15</v>
       </c>
       <c r="W41">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>9.845231917910249</v>
+        <v>9.294082953533779</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1014704647008414</v>
+        <v>0.101378171406106</v>
       </c>
       <c r="C42">
-        <v>4.402838157525953</v>
+        <v>4.342859360150468</v>
       </c>
       <c r="D42">
-        <v>6.681638157525954</v>
+        <v>6.688529360150469</v>
       </c>
       <c r="E42">
-        <v>1.8678</v>
+        <v>1.934670000000001</v>
       </c>
       <c r="F42">
-        <v>2.6748</v>
+        <v>2.74167</v>
       </c>
       <c r="G42">
         <v>0.396</v>
@@ -4731,28 +4731,28 @@
         <v>1.33</v>
       </c>
       <c r="M42">
-        <v>0.1431018</v>
+        <v>0.146679345</v>
       </c>
       <c r="N42">
-        <v>1.1868982</v>
+        <v>1.183320655</v>
       </c>
       <c r="O42">
-        <v>0.17803473</v>
+        <v>0.17749809825</v>
       </c>
       <c r="P42">
-        <v>1.00886347</v>
+        <v>1.00582255675</v>
       </c>
       <c r="Q42">
-        <v>1.16886347</v>
+        <v>1.16582255675</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1388007745014023</v>
+        <v>0.1402261379764508</v>
       </c>
       <c r="T42">
-        <v>1.212111858385599</v>
+        <v>1.230689122713542</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.294082953533779</v>
+        <v>9.067398003447588</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.101378171406106</v>
+        <v>0.1012858781113706</v>
       </c>
       <c r="C43">
-        <v>4.342859360150468</v>
+        <v>4.282894792130474</v>
       </c>
       <c r="D43">
-        <v>6.688529360150469</v>
+        <v>6.695434792130474</v>
       </c>
       <c r="E43">
-        <v>1.934670000000001</v>
+        <v>2.00154</v>
       </c>
       <c r="F43">
-        <v>2.74167</v>
+        <v>2.80854</v>
       </c>
       <c r="G43">
         <v>0.396</v>
@@ -4813,28 +4813,28 @@
         <v>1.33</v>
       </c>
       <c r="M43">
-        <v>0.146679345</v>
+        <v>0.15025689</v>
       </c>
       <c r="N43">
-        <v>1.183320655</v>
+        <v>1.17974311</v>
       </c>
       <c r="O43">
-        <v>0.17749809825</v>
+        <v>0.1769614665</v>
       </c>
       <c r="P43">
-        <v>1.00582255675</v>
+        <v>1.0027816435</v>
       </c>
       <c r="Q43">
-        <v>1.16582255675</v>
+        <v>1.1627816435</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1402261379764508</v>
+        <v>0.1417006519161562</v>
       </c>
       <c r="T43">
-        <v>1.230689122713542</v>
+        <v>1.249906982363139</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.067398003447588</v>
+        <v>8.851507574794073</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1012858781113706</v>
+        <v>0.1011935848166352</v>
       </c>
       <c r="C44">
-        <v>4.282894792130474</v>
+        <v>4.222944497583915</v>
       </c>
       <c r="D44">
-        <v>6.695434792130474</v>
+        <v>6.702354497583916</v>
       </c>
       <c r="E44">
-        <v>2.00154</v>
+        <v>2.06841</v>
       </c>
       <c r="F44">
-        <v>2.80854</v>
+        <v>2.87541</v>
       </c>
       <c r="G44">
         <v>0.396</v>
@@ -4895,28 +4895,28 @@
         <v>1.33</v>
       </c>
       <c r="M44">
-        <v>0.15025689</v>
+        <v>0.153834435</v>
       </c>
       <c r="N44">
-        <v>1.17974311</v>
+        <v>1.176165565</v>
       </c>
       <c r="O44">
-        <v>0.1769614665</v>
+        <v>0.17642483475</v>
       </c>
       <c r="P44">
-        <v>1.0027816435</v>
+        <v>0.99974073025</v>
       </c>
       <c r="Q44">
-        <v>1.1627816435</v>
+        <v>1.15974073025</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1417006519161562</v>
+        <v>0.1432269031870793</v>
       </c>
       <c r="T44">
-        <v>1.249906982363139</v>
+        <v>1.269799152877634</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.851507574794075</v>
+        <v>8.645658561426771</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1011935848166352</v>
+        <v>0.1011012915218998</v>
       </c>
       <c r="C45">
-        <v>4.222944497583915</v>
+        <v>4.163008520811315</v>
       </c>
       <c r="D45">
-        <v>6.702354497583916</v>
+        <v>6.709288520811316</v>
       </c>
       <c r="E45">
-        <v>2.06841</v>
+        <v>2.13528</v>
       </c>
       <c r="F45">
-        <v>2.87541</v>
+        <v>2.94228</v>
       </c>
       <c r="G45">
         <v>0.396</v>
@@ -4977,28 +4977,28 @@
         <v>1.33</v>
       </c>
       <c r="M45">
-        <v>0.153834435</v>
+        <v>0.15741198</v>
       </c>
       <c r="N45">
-        <v>1.176165565</v>
+        <v>1.17258802</v>
       </c>
       <c r="O45">
-        <v>0.17642483475</v>
+        <v>0.175888203</v>
       </c>
       <c r="P45">
-        <v>0.99974073025</v>
+        <v>0.9966998170000001</v>
       </c>
       <c r="Q45">
-        <v>1.15974073025</v>
+        <v>1.156699817</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1432269031870793</v>
+        <v>0.1448076634319639</v>
       </c>
       <c r="T45">
-        <v>1.269799152877634</v>
+        <v>1.290401758053361</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.645658561426771</v>
+        <v>8.449166321394344</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1011012915218998</v>
+        <v>0.1010089982271644</v>
       </c>
       <c r="C46">
-        <v>4.163008520811315</v>
+        <v>4.10308690629671</v>
       </c>
       <c r="D46">
-        <v>6.709288520811316</v>
+        <v>6.71623690629671</v>
       </c>
       <c r="E46">
-        <v>2.13528</v>
+        <v>2.20215</v>
       </c>
       <c r="F46">
-        <v>2.94228</v>
+        <v>3.00915</v>
       </c>
       <c r="G46">
         <v>0.396</v>
@@ -5059,28 +5059,28 @@
         <v>1.33</v>
       </c>
       <c r="M46">
-        <v>0.15741198</v>
+        <v>0.160989525</v>
       </c>
       <c r="N46">
-        <v>1.17258802</v>
+        <v>1.169010475</v>
       </c>
       <c r="O46">
-        <v>0.175888203</v>
+        <v>0.17535157125</v>
       </c>
       <c r="P46">
-        <v>0.9966998170000001</v>
+        <v>0.9936589037500001</v>
       </c>
       <c r="Q46">
-        <v>1.156699817</v>
+        <v>1.15365890375</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1448076634319639</v>
+        <v>0.1464459058675717</v>
       </c>
       <c r="T46">
-        <v>1.290401758053361</v>
+        <v>1.311753548871842</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.449166321394344</v>
+        <v>8.261407069807802</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1010089982271644</v>
+        <v>0.100916704932429</v>
       </c>
       <c r="C47">
-        <v>4.10308690629671</v>
+        <v>4.043179698708604</v>
       </c>
       <c r="D47">
-        <v>6.71623690629671</v>
+        <v>6.723199698708605</v>
       </c>
       <c r="E47">
-        <v>2.20215</v>
+        <v>2.26902</v>
       </c>
       <c r="F47">
-        <v>3.00915</v>
+        <v>3.07602</v>
       </c>
       <c r="G47">
         <v>0.396</v>
@@ -5141,28 +5141,28 @@
         <v>1.33</v>
       </c>
       <c r="M47">
-        <v>0.160989525</v>
+        <v>0.16456707</v>
       </c>
       <c r="N47">
-        <v>1.169010475</v>
+        <v>1.16543293</v>
       </c>
       <c r="O47">
-        <v>0.17535157125</v>
+        <v>0.1748149395</v>
       </c>
       <c r="P47">
-        <v>0.9936589037500001</v>
+        <v>0.9906179905000001</v>
       </c>
       <c r="Q47">
-        <v>1.15365890375</v>
+        <v>1.1506179905</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1464459058675717</v>
+        <v>0.1481448239489427</v>
       </c>
       <c r="T47">
-        <v>1.311753548871842</v>
+        <v>1.333896146757674</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.261407069807802</v>
+        <v>8.081811263942416</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.100916704932429</v>
+        <v>0.1008244116376937</v>
       </c>
       <c r="C48">
-        <v>4.043179698708604</v>
+        <v>3.98328694290093</v>
       </c>
       <c r="D48">
-        <v>6.723199698708605</v>
+        <v>6.730176942900931</v>
       </c>
       <c r="E48">
-        <v>2.26902</v>
+        <v>2.33589</v>
       </c>
       <c r="F48">
-        <v>3.07602</v>
+        <v>3.14289</v>
       </c>
       <c r="G48">
         <v>0.396</v>
@@ -5223,28 +5223,28 @@
         <v>1.33</v>
       </c>
       <c r="M48">
-        <v>0.16456707</v>
+        <v>0.168144615</v>
       </c>
       <c r="N48">
-        <v>1.16543293</v>
+        <v>1.161855385</v>
       </c>
       <c r="O48">
-        <v>0.1748149395</v>
+        <v>0.17427830775</v>
       </c>
       <c r="P48">
-        <v>0.9906179905000001</v>
+        <v>0.98757707725</v>
       </c>
       <c r="Q48">
-        <v>1.1506179905</v>
+        <v>1.14757707725</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1481448239489427</v>
+        <v>0.1499078521465918</v>
       </c>
       <c r="T48">
-        <v>1.333896146757674</v>
+        <v>1.356874314375047</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.081811263942416</v>
+        <v>7.909857832794703</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1008244116376937</v>
+        <v>0.1007321183429583</v>
       </c>
       <c r="C49">
-        <v>3.98328694290093</v>
+        <v>3.923408683914004</v>
       </c>
       <c r="D49">
-        <v>6.730176942900931</v>
+        <v>6.737168683914004</v>
       </c>
       <c r="E49">
-        <v>2.33589</v>
+        <v>2.40276</v>
       </c>
       <c r="F49">
-        <v>3.14289</v>
+        <v>3.20976</v>
       </c>
       <c r="G49">
         <v>0.396</v>
@@ -5305,28 +5305,28 @@
         <v>1.33</v>
       </c>
       <c r="M49">
-        <v>0.168144615</v>
+        <v>0.17172216</v>
       </c>
       <c r="N49">
-        <v>1.161855385</v>
+        <v>1.15827784</v>
       </c>
       <c r="O49">
-        <v>0.17427830775</v>
+        <v>0.173741676</v>
       </c>
       <c r="P49">
-        <v>0.98757707725</v>
+        <v>0.984536164</v>
       </c>
       <c r="Q49">
-        <v>1.14757707725</v>
+        <v>1.144536164</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1499078521465918</v>
+        <v>0.1517386891210736</v>
       </c>
       <c r="T49">
-        <v>1.356874314375047</v>
+        <v>1.380736257670011</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.909857832794703</v>
+        <v>7.745069127944815</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1007321183429583</v>
+        <v>0.1009730250482229</v>
       </c>
       <c r="C50">
-        <v>3.923408683914004</v>
+        <v>3.838319079707117</v>
       </c>
       <c r="D50">
-        <v>6.737168683914004</v>
+        <v>6.718949079707117</v>
       </c>
       <c r="E50">
-        <v>2.40276</v>
+        <v>2.46963</v>
       </c>
       <c r="F50">
-        <v>3.20976</v>
+        <v>3.27663</v>
       </c>
       <c r="G50">
         <v>0.396</v>
@@ -5387,45 +5387,45 @@
         <v>1.33</v>
       </c>
       <c r="M50">
-        <v>0.17172216</v>
+        <v>0.177921009</v>
       </c>
       <c r="N50">
-        <v>1.15827784</v>
+        <v>1.152078991</v>
       </c>
       <c r="O50">
-        <v>0.173741676</v>
+        <v>0.17281184865</v>
       </c>
       <c r="P50">
-        <v>0.984536164</v>
+        <v>0.97926714235</v>
       </c>
       <c r="Q50">
-        <v>1.144536164</v>
+        <v>1.13926714235</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1517386891210736</v>
+        <v>0.1536413236239664</v>
       </c>
       <c r="T50">
-        <v>1.380736257670011</v>
+        <v>1.40553396344713</v>
       </c>
       <c r="U50">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V50">
         <v>0.15</v>
       </c>
       <c r="W50">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y50">
-        <v>7.745069127944815</v>
+        <v>7.475227391499337</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1009730250482229</v>
+        <v>0.1008875317534875</v>
       </c>
       <c r="C51">
-        <v>3.838319079707117</v>
+        <v>3.777903586085985</v>
       </c>
       <c r="D51">
-        <v>6.718949079707117</v>
+        <v>6.725403586085985</v>
       </c>
       <c r="E51">
-        <v>2.46963</v>
+        <v>2.5365</v>
       </c>
       <c r="F51">
-        <v>3.27663</v>
+        <v>3.3435</v>
       </c>
       <c r="G51">
         <v>0.396</v>
@@ -5469,28 +5469,28 @@
         <v>1.33</v>
       </c>
       <c r="M51">
-        <v>0.177921009</v>
+        <v>0.18155205</v>
       </c>
       <c r="N51">
-        <v>1.152078991</v>
+        <v>1.14844795</v>
       </c>
       <c r="O51">
-        <v>0.17281184865</v>
+        <v>0.1722671925</v>
       </c>
       <c r="P51">
-        <v>0.97926714235</v>
+        <v>0.9761807575</v>
       </c>
       <c r="Q51">
-        <v>1.13926714235</v>
+        <v>1.1361807575</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1536413236239664</v>
+        <v>0.155620063506975</v>
       </c>
       <c r="T51">
-        <v>1.40553396344713</v>
+        <v>1.431323577455335</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.475227391499337</v>
+        <v>7.325722843669349</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1008875317534875</v>
+        <v>0.1008020384587521</v>
       </c>
       <c r="C52">
-        <v>3.777903586085985</v>
+        <v>3.717500505332272</v>
       </c>
       <c r="D52">
-        <v>6.725403586085985</v>
+        <v>6.731870505332273</v>
       </c>
       <c r="E52">
-        <v>2.5365</v>
+        <v>2.60337</v>
       </c>
       <c r="F52">
-        <v>3.3435</v>
+        <v>3.41037</v>
       </c>
       <c r="G52">
         <v>0.396</v>
@@ -5551,28 +5551,28 @@
         <v>1.33</v>
       </c>
       <c r="M52">
-        <v>0.18155205</v>
+        <v>0.185183091</v>
       </c>
       <c r="N52">
-        <v>1.14844795</v>
+        <v>1.144816909</v>
       </c>
       <c r="O52">
-        <v>0.1722671925</v>
+        <v>0.17172253635</v>
       </c>
       <c r="P52">
-        <v>0.9761807575</v>
+        <v>0.97309437265</v>
       </c>
       <c r="Q52">
-        <v>1.1361807575</v>
+        <v>1.13309437265</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.155620063506975</v>
+        <v>0.1576795682831676</v>
       </c>
       <c r="T52">
-        <v>1.431323577455335</v>
+        <v>1.458165828769996</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.325722843669349</v>
+        <v>7.182081219283676</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1008020384587521</v>
+        <v>0.1007165451640167</v>
       </c>
       <c r="C53">
-        <v>3.717500505332272</v>
+        <v>3.657109873287817</v>
       </c>
       <c r="D53">
-        <v>6.731870505332273</v>
+        <v>6.738349873287818</v>
       </c>
       <c r="E53">
-        <v>2.60337</v>
+        <v>2.67024</v>
       </c>
       <c r="F53">
-        <v>3.41037</v>
+        <v>3.47724</v>
       </c>
       <c r="G53">
         <v>0.396</v>
@@ -5633,28 +5633,28 @@
         <v>1.33</v>
       </c>
       <c r="M53">
-        <v>0.185183091</v>
+        <v>0.188814132</v>
       </c>
       <c r="N53">
-        <v>1.144816909</v>
+        <v>1.141185868</v>
       </c>
       <c r="O53">
-        <v>0.17172253635</v>
+        <v>0.1711778802</v>
       </c>
       <c r="P53">
-        <v>0.97309437265</v>
+        <v>0.9700079878</v>
       </c>
       <c r="Q53">
-        <v>1.13309437265</v>
+        <v>1.1300079878</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1576795682831676</v>
+        <v>0.1598248857583682</v>
       </c>
       <c r="T53">
-        <v>1.458165828769996</v>
+        <v>1.486126507222769</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.182081219283676</v>
+        <v>7.04396427275899</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1007165451640167</v>
+        <v>0.1006310518692814</v>
       </c>
       <c r="C54">
-        <v>3.657109873287817</v>
+        <v>3.596731725932577</v>
       </c>
       <c r="D54">
-        <v>6.738349873287818</v>
+        <v>6.744841725932577</v>
       </c>
       <c r="E54">
-        <v>2.67024</v>
+        <v>2.73711</v>
       </c>
       <c r="F54">
-        <v>3.47724</v>
+        <v>3.54411</v>
       </c>
       <c r="G54">
         <v>0.396</v>
@@ -5715,28 +5715,28 @@
         <v>1.33</v>
       </c>
       <c r="M54">
-        <v>0.188814132</v>
+        <v>0.192445173</v>
       </c>
       <c r="N54">
-        <v>1.141185868</v>
+        <v>1.137554827</v>
       </c>
       <c r="O54">
-        <v>0.1711778802</v>
+        <v>0.17063322405</v>
       </c>
       <c r="P54">
-        <v>0.9700079878</v>
+        <v>0.96692160295</v>
       </c>
       <c r="Q54">
-        <v>1.1300079878</v>
+        <v>1.12692160295</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1598248857583682</v>
+        <v>0.1620614933388965</v>
       </c>
       <c r="T54">
-        <v>1.486126507222769</v>
+        <v>1.515277001779914</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.04396427275899</v>
+        <v>6.911059286480518</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1006310518692814</v>
+        <v>0.100545558574546</v>
       </c>
       <c r="C55">
-        <v>3.596731725932577</v>
+        <v>3.536366099385304</v>
       </c>
       <c r="D55">
-        <v>6.744841725932577</v>
+        <v>6.751346099385304</v>
       </c>
       <c r="E55">
-        <v>2.73711</v>
+        <v>2.803980000000001</v>
       </c>
       <c r="F55">
-        <v>3.54411</v>
+        <v>3.610980000000001</v>
       </c>
       <c r="G55">
         <v>0.396</v>
@@ -5797,28 +5797,28 @@
         <v>1.33</v>
       </c>
       <c r="M55">
-        <v>0.192445173</v>
+        <v>0.196076214</v>
       </c>
       <c r="N55">
-        <v>1.137554827</v>
+        <v>1.133923786</v>
       </c>
       <c r="O55">
-        <v>0.17063322405</v>
+        <v>0.1700885679</v>
       </c>
       <c r="P55">
-        <v>0.96692160295</v>
+        <v>0.9638352181000001</v>
       </c>
       <c r="Q55">
-        <v>1.12692160295</v>
+        <v>1.1238352181</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1620614933388965</v>
+        <v>0.1643953447272738</v>
       </c>
       <c r="T55">
-        <v>1.515277001779914</v>
+        <v>1.545694909143892</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.911059286480518</v>
+        <v>6.783076707101249</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.100545558574546</v>
+        <v>0.1004600652798106</v>
       </c>
       <c r="C56">
-        <v>3.536366099385304</v>
+        <v>3.476013029904201</v>
       </c>
       <c r="D56">
-        <v>6.751346099385304</v>
+        <v>6.757863029904201</v>
       </c>
       <c r="E56">
-        <v>2.803980000000001</v>
+        <v>2.87085</v>
       </c>
       <c r="F56">
-        <v>3.610980000000001</v>
+        <v>3.67785</v>
       </c>
       <c r="G56">
         <v>0.396</v>
@@ -5879,28 +5879,28 @@
         <v>1.33</v>
       </c>
       <c r="M56">
-        <v>0.196076214</v>
+        <v>0.199707255</v>
       </c>
       <c r="N56">
-        <v>1.133923786</v>
+        <v>1.130292745</v>
       </c>
       <c r="O56">
-        <v>0.1700885679</v>
+        <v>0.16954391175</v>
       </c>
       <c r="P56">
-        <v>0.9638352181000001</v>
+        <v>0.96074883325</v>
       </c>
       <c r="Q56">
-        <v>1.1238352181</v>
+        <v>1.12074883325</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1643953447272738</v>
+        <v>0.1668329228440235</v>
       </c>
       <c r="T56">
-        <v>1.545694909143892</v>
+        <v>1.577464723501825</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.783076707101249</v>
+        <v>6.659748039699408</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1004600652798106</v>
+        <v>0.1003745719850752</v>
       </c>
       <c r="C57">
-        <v>3.476013029904201</v>
+        <v>3.41567255388761</v>
       </c>
       <c r="D57">
-        <v>6.757863029904201</v>
+        <v>6.76439255388761</v>
       </c>
       <c r="E57">
-        <v>2.87085</v>
+        <v>2.937720000000001</v>
       </c>
       <c r="F57">
-        <v>3.67785</v>
+        <v>3.74472</v>
       </c>
       <c r="G57">
         <v>0.396</v>
@@ -5961,28 +5961,28 @@
         <v>1.33</v>
       </c>
       <c r="M57">
-        <v>0.199707255</v>
+        <v>0.203338296</v>
       </c>
       <c r="N57">
-        <v>1.130292745</v>
+        <v>1.126661704</v>
       </c>
       <c r="O57">
-        <v>0.16954391175</v>
+        <v>0.1689992556</v>
       </c>
       <c r="P57">
-        <v>0.96074883325</v>
+        <v>0.9576624484</v>
       </c>
       <c r="Q57">
-        <v>1.12074883325</v>
+        <v>1.1176624484</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1668329228440235</v>
+        <v>0.16938129996608</v>
       </c>
       <c r="T57">
-        <v>1.577464723501825</v>
+        <v>1.610678620330573</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.659748039699408</v>
+        <v>6.540823967561919</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1003745719850752</v>
+        <v>0.1002890786903398</v>
       </c>
       <c r="C58">
-        <v>3.41567255388761</v>
+        <v>3.355344707874679</v>
       </c>
       <c r="D58">
-        <v>6.76439255388761</v>
+        <v>6.77093470787468</v>
       </c>
       <c r="E58">
-        <v>2.937720000000001</v>
+        <v>3.004590000000001</v>
       </c>
       <c r="F58">
-        <v>3.74472</v>
+        <v>3.811590000000001</v>
       </c>
       <c r="G58">
         <v>0.396</v>
@@ -6043,28 +6043,28 @@
         <v>1.33</v>
       </c>
       <c r="M58">
-        <v>0.203338296</v>
+        <v>0.206969337</v>
       </c>
       <c r="N58">
-        <v>1.126661704</v>
+        <v>1.123030663</v>
       </c>
       <c r="O58">
-        <v>0.1689992556</v>
+        <v>0.16845459945</v>
       </c>
       <c r="P58">
-        <v>0.9576624484</v>
+        <v>0.95457606355</v>
       </c>
       <c r="Q58">
-        <v>1.1176624484</v>
+        <v>1.11457606355</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.16938129996608</v>
+        <v>0.1720482062566042</v>
       </c>
       <c r="T58">
-        <v>1.610678620330573</v>
+        <v>1.64543734956996</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.540823967561919</v>
+        <v>6.426072669885394</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1002890786903398</v>
+        <v>0.1002035853956044</v>
       </c>
       <c r="C59">
-        <v>3.355344707874679</v>
+        <v>3.295029528546054</v>
       </c>
       <c r="D59">
-        <v>6.77093470787468</v>
+        <v>6.777489528546054</v>
       </c>
       <c r="E59">
-        <v>3.004590000000001</v>
+        <v>3.071460000000001</v>
       </c>
       <c r="F59">
-        <v>3.811590000000001</v>
+        <v>3.87846</v>
       </c>
       <c r="G59">
         <v>0.396</v>
@@ -6125,28 +6125,28 @@
         <v>1.33</v>
       </c>
       <c r="M59">
-        <v>0.206969337</v>
+        <v>0.210600378</v>
       </c>
       <c r="N59">
-        <v>1.123030663</v>
+        <v>1.119399622</v>
       </c>
       <c r="O59">
-        <v>0.16845459945</v>
+        <v>0.1679099433</v>
       </c>
       <c r="P59">
-        <v>0.95457606355</v>
+        <v>0.9514896787</v>
       </c>
       <c r="Q59">
-        <v>1.11457606355</v>
+        <v>1.1114896787</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1720482062566042</v>
+        <v>0.1748421080847725</v>
       </c>
       <c r="T59">
-        <v>1.64543734956996</v>
+        <v>1.681851256392176</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.426072669885394</v>
+        <v>6.31527831350806</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1002035853956044</v>
+        <v>0.100118092100869</v>
       </c>
       <c r="C60">
-        <v>3.295029528546053</v>
+        <v>3.234727052724549</v>
       </c>
       <c r="D60">
-        <v>6.777489528546053</v>
+        <v>6.784057052724549</v>
       </c>
       <c r="E60">
-        <v>3.07146</v>
+        <v>3.13833</v>
       </c>
       <c r="F60">
-        <v>3.87846</v>
+        <v>3.94533</v>
       </c>
       <c r="G60">
         <v>0.396</v>
@@ -6207,28 +6207,28 @@
         <v>1.33</v>
       </c>
       <c r="M60">
-        <v>0.210600378</v>
+        <v>0.214231419</v>
       </c>
       <c r="N60">
-        <v>1.119399622</v>
+        <v>1.115768581</v>
       </c>
       <c r="O60">
-        <v>0.1679099433</v>
+        <v>0.16736528715</v>
       </c>
       <c r="P60">
-        <v>0.9514896787</v>
+        <v>0.9484032938500002</v>
       </c>
       <c r="Q60">
-        <v>1.1114896787</v>
+        <v>1.10840329385</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1748421080847724</v>
+        <v>0.1777722978069976</v>
       </c>
       <c r="T60">
-        <v>1.681851256392175</v>
+        <v>1.720041451352059</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.31527831350806</v>
+        <v>6.208239698024874</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.100118092100869</v>
+        <v>0.1005425988061336</v>
       </c>
       <c r="C61">
-        <v>3.234727052724549</v>
+        <v>3.135371504752974</v>
       </c>
       <c r="D61">
-        <v>6.784057052724549</v>
+        <v>6.751571504752974</v>
       </c>
       <c r="E61">
-        <v>3.13833</v>
+        <v>3.2052</v>
       </c>
       <c r="F61">
-        <v>3.94533</v>
+        <v>4.0122</v>
       </c>
       <c r="G61">
         <v>0.396</v>
@@ -6289,45 +6289,45 @@
         <v>1.33</v>
       </c>
       <c r="M61">
-        <v>0.214231419</v>
+        <v>0.22187466</v>
       </c>
       <c r="N61">
-        <v>1.115768581</v>
+        <v>1.10812534</v>
       </c>
       <c r="O61">
-        <v>0.16736528715</v>
+        <v>0.166218801</v>
       </c>
       <c r="P61">
-        <v>0.9484032938500002</v>
+        <v>0.941906539</v>
       </c>
       <c r="Q61">
-        <v>1.10840329385</v>
+        <v>1.101906539</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1777722978069976</v>
+        <v>0.1808489970153341</v>
       </c>
       <c r="T61">
-        <v>1.720041451352059</v>
+        <v>1.760141156059938</v>
       </c>
       <c r="U61">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V61">
         <v>0.15</v>
       </c>
       <c r="W61">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y61">
-        <v>6.208239698024874</v>
+        <v>5.994375382930164</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1005425988061336</v>
+        <v>0.1004656055113983</v>
       </c>
       <c r="C62">
-        <v>3.135371504752974</v>
+        <v>3.074370331310443</v>
       </c>
       <c r="D62">
-        <v>6.751571504752974</v>
+        <v>6.757440331310443</v>
       </c>
       <c r="E62">
-        <v>3.2052</v>
+        <v>3.27207</v>
       </c>
       <c r="F62">
-        <v>4.0122</v>
+        <v>4.07907</v>
       </c>
       <c r="G62">
         <v>0.396</v>
@@ -6371,28 +6371,28 @@
         <v>1.33</v>
       </c>
       <c r="M62">
-        <v>0.22187466</v>
+        <v>0.225572571</v>
       </c>
       <c r="N62">
-        <v>1.10812534</v>
+        <v>1.104427429</v>
       </c>
       <c r="O62">
-        <v>0.166218801</v>
+        <v>0.16566411435</v>
       </c>
       <c r="P62">
-        <v>0.941906539</v>
+        <v>0.9387633146500001</v>
       </c>
       <c r="Q62">
-        <v>1.101906539</v>
+        <v>1.09876331465</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1808489970153341</v>
+        <v>0.184083475670252</v>
       </c>
       <c r="T62">
-        <v>1.760141156059938</v>
+        <v>1.802297255881041</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.994375382930164</v>
+        <v>5.89610693402967</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1004656055113983</v>
+        <v>0.1003886122166629</v>
       </c>
       <c r="C63">
-        <v>3.074370331310443</v>
+        <v>3.013379369739619</v>
       </c>
       <c r="D63">
-        <v>6.757440331310443</v>
+        <v>6.763319369739619</v>
       </c>
       <c r="E63">
-        <v>3.27207</v>
+        <v>3.33894</v>
       </c>
       <c r="F63">
-        <v>4.07907</v>
+        <v>4.14594</v>
       </c>
       <c r="G63">
         <v>0.396</v>
@@ -6453,28 +6453,28 @@
         <v>1.33</v>
       </c>
       <c r="M63">
-        <v>0.225572571</v>
+        <v>0.229270482</v>
       </c>
       <c r="N63">
-        <v>1.104427429</v>
+        <v>1.100729518</v>
       </c>
       <c r="O63">
-        <v>0.16566411435</v>
+        <v>0.1651094277</v>
       </c>
       <c r="P63">
-        <v>0.9387633146500001</v>
+        <v>0.9356200903</v>
       </c>
       <c r="Q63">
-        <v>1.09876331465</v>
+        <v>1.0956200903</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.184083475670252</v>
+        <v>0.1874881900438497</v>
       </c>
       <c r="T63">
-        <v>1.802297255881041</v>
+        <v>1.846672097797992</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.89610693402967</v>
+        <v>5.801008435093707</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1003886122166629</v>
+        <v>0.1003116189219275</v>
       </c>
       <c r="C64">
-        <v>3.013379369739619</v>
+        <v>2.952398646716994</v>
       </c>
       <c r="D64">
-        <v>6.763319369739619</v>
+        <v>6.769208646716995</v>
       </c>
       <c r="E64">
-        <v>3.33894</v>
+        <v>3.40581</v>
       </c>
       <c r="F64">
-        <v>4.14594</v>
+        <v>4.21281</v>
       </c>
       <c r="G64">
         <v>0.396</v>
@@ -6535,28 +6535,28 @@
         <v>1.33</v>
       </c>
       <c r="M64">
-        <v>0.229270482</v>
+        <v>0.232968393</v>
       </c>
       <c r="N64">
-        <v>1.100729518</v>
+        <v>1.097031607</v>
       </c>
       <c r="O64">
-        <v>0.1651094277</v>
+        <v>0.16455474105</v>
       </c>
       <c r="P64">
-        <v>0.9356200903</v>
+        <v>0.9324768659500001</v>
       </c>
       <c r="Q64">
-        <v>1.0956200903</v>
+        <v>1.09247686595</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1874881900438497</v>
+        <v>0.1910769430322365</v>
       </c>
       <c r="T64">
-        <v>1.846672097797992</v>
+        <v>1.893445579818561</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.801008435093707</v>
+        <v>5.708928936123966</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1003116189219275</v>
+        <v>0.1002346256271921</v>
       </c>
       <c r="C65">
-        <v>2.952398646716994</v>
+        <v>2.891428189012055</v>
       </c>
       <c r="D65">
-        <v>6.769208646716995</v>
+        <v>6.775108189012055</v>
       </c>
       <c r="E65">
-        <v>3.40581</v>
+        <v>3.47268</v>
       </c>
       <c r="F65">
-        <v>4.21281</v>
+        <v>4.27968</v>
       </c>
       <c r="G65">
         <v>0.396</v>
@@ -6617,28 +6617,28 @@
         <v>1.33</v>
       </c>
       <c r="M65">
-        <v>0.232968393</v>
+        <v>0.236666304</v>
       </c>
       <c r="N65">
-        <v>1.097031607</v>
+        <v>1.093333696</v>
       </c>
       <c r="O65">
-        <v>0.16455474105</v>
+        <v>0.1640000544</v>
       </c>
       <c r="P65">
-        <v>0.9324768659500001</v>
+        <v>0.9293336416000002</v>
       </c>
       <c r="Q65">
-        <v>1.09247686595</v>
+        <v>1.0893336416</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1910769430322365</v>
+        <v>0.1948650711866448</v>
       </c>
       <c r="T65">
-        <v>1.893445579818561</v>
+        <v>1.942817588618051</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.708928936123966</v>
+        <v>5.61972692149703</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1002346256271921</v>
+        <v>0.1001576323324567</v>
       </c>
       <c r="C66">
-        <v>2.891428189012055</v>
+        <v>2.830468023487687</v>
       </c>
       <c r="D66">
-        <v>6.775108189012055</v>
+        <v>6.781018023487688</v>
       </c>
       <c r="E66">
-        <v>3.47268</v>
+        <v>3.539550000000001</v>
       </c>
       <c r="F66">
-        <v>4.27968</v>
+        <v>4.346550000000001</v>
       </c>
       <c r="G66">
         <v>0.396</v>
@@ -6699,28 +6699,28 @@
         <v>1.33</v>
       </c>
       <c r="M66">
-        <v>0.236666304</v>
+        <v>0.240364215</v>
       </c>
       <c r="N66">
-        <v>1.093333696</v>
+        <v>1.089635785</v>
       </c>
       <c r="O66">
-        <v>0.1640000544</v>
+        <v>0.16344536775</v>
       </c>
       <c r="P66">
-        <v>0.9293336416000002</v>
+        <v>0.9261904172500001</v>
       </c>
       <c r="Q66">
-        <v>1.0893336416</v>
+        <v>1.08619041725</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1948650711866448</v>
+        <v>0.1988696638070192</v>
       </c>
       <c r="T66">
-        <v>1.942817588618051</v>
+        <v>1.995010855063227</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.61972692149703</v>
+        <v>5.533269584243228</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1001576323324567</v>
+        <v>0.1000806390377213</v>
       </c>
       <c r="C67">
-        <v>2.830468023487687</v>
+        <v>2.769518177100594</v>
       </c>
       <c r="D67">
-        <v>6.781018023487688</v>
+        <v>6.786938177100595</v>
       </c>
       <c r="E67">
-        <v>3.539550000000001</v>
+        <v>3.60642</v>
       </c>
       <c r="F67">
-        <v>4.346550000000001</v>
+        <v>4.41342</v>
       </c>
       <c r="G67">
         <v>0.396</v>
@@ -6781,28 +6781,28 @@
         <v>1.33</v>
       </c>
       <c r="M67">
-        <v>0.240364215</v>
+        <v>0.244062126</v>
       </c>
       <c r="N67">
-        <v>1.089635785</v>
+        <v>1.085937874</v>
       </c>
       <c r="O67">
-        <v>0.16344536775</v>
+        <v>0.1628906811</v>
       </c>
       <c r="P67">
-        <v>0.9261904172500001</v>
+        <v>0.9230471929</v>
       </c>
       <c r="Q67">
-        <v>1.08619041725</v>
+        <v>1.0830471929</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1988696638070192</v>
+        <v>0.2031098206991804</v>
       </c>
       <c r="T67">
-        <v>1.995010855063227</v>
+        <v>2.050274313652236</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.533269584243228</v>
+        <v>5.449432166300149</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1000806390377213</v>
+        <v>0.100003645742986</v>
       </c>
       <c r="C68">
-        <v>2.769518177100594</v>
+        <v>2.708578676901698</v>
       </c>
       <c r="D68">
-        <v>6.786938177100595</v>
+        <v>6.792868676901698</v>
       </c>
       <c r="E68">
-        <v>3.60642</v>
+        <v>3.67329</v>
       </c>
       <c r="F68">
-        <v>4.41342</v>
+        <v>4.48029</v>
       </c>
       <c r="G68">
         <v>0.396</v>
@@ -6863,28 +6863,28 @@
         <v>1.33</v>
       </c>
       <c r="M68">
-        <v>0.244062126</v>
+        <v>0.247760037</v>
       </c>
       <c r="N68">
-        <v>1.085937874</v>
+        <v>1.082239963</v>
       </c>
       <c r="O68">
-        <v>0.1628906811</v>
+        <v>0.16233599445</v>
       </c>
       <c r="P68">
-        <v>0.9230471929</v>
+        <v>0.9199039685500001</v>
       </c>
       <c r="Q68">
-        <v>1.0830471929</v>
+        <v>1.07990396855</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2031098206991804</v>
+        <v>0.2076069567969271</v>
       </c>
       <c r="T68">
-        <v>2.050274313652236</v>
+        <v>2.108887072761791</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.449432166300149</v>
+        <v>5.368097357847908</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.100003645742986</v>
+        <v>0.09992665244825057</v>
       </c>
       <c r="C69">
-        <v>2.708578676901698</v>
+        <v>2.647649550036548</v>
       </c>
       <c r="D69">
-        <v>6.792868676901698</v>
+        <v>6.798809550036549</v>
       </c>
       <c r="E69">
-        <v>3.67329</v>
+        <v>3.740160000000001</v>
       </c>
       <c r="F69">
-        <v>4.48029</v>
+        <v>4.547160000000001</v>
       </c>
       <c r="G69">
         <v>0.396</v>
@@ -6945,28 +6945,28 @@
         <v>1.33</v>
       </c>
       <c r="M69">
-        <v>0.247760037</v>
+        <v>0.251457948</v>
       </c>
       <c r="N69">
-        <v>1.082239963</v>
+        <v>1.078542052</v>
       </c>
       <c r="O69">
-        <v>0.16233599445</v>
+        <v>0.1617813078</v>
       </c>
       <c r="P69">
-        <v>0.9199039685500001</v>
+        <v>0.9167607442</v>
       </c>
       <c r="Q69">
-        <v>1.07990396855</v>
+        <v>1.0767607442</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2076069567969271</v>
+        <v>0.212385163900783</v>
       </c>
       <c r="T69">
-        <v>2.108887072761791</v>
+        <v>2.171163129315693</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.368097357847908</v>
+        <v>5.289154749644262</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09992665244825057</v>
+        <v>0.09984965915351518</v>
       </c>
       <c r="C70">
-        <v>2.647649550036548</v>
+        <v>2.586730823745745</v>
       </c>
       <c r="D70">
-        <v>6.798809550036549</v>
+        <v>6.804760823745745</v>
       </c>
       <c r="E70">
-        <v>3.740160000000001</v>
+        <v>3.807030000000001</v>
       </c>
       <c r="F70">
-        <v>4.547160000000001</v>
+        <v>4.614030000000001</v>
       </c>
       <c r="G70">
         <v>0.396</v>
@@ -7027,28 +7027,28 @@
         <v>1.33</v>
       </c>
       <c r="M70">
-        <v>0.251457948</v>
+        <v>0.255155859</v>
       </c>
       <c r="N70">
-        <v>1.078542052</v>
+        <v>1.074844141</v>
       </c>
       <c r="O70">
-        <v>0.1617813078</v>
+        <v>0.16122662115</v>
       </c>
       <c r="P70">
-        <v>0.9167607442</v>
+        <v>0.9136175198500001</v>
       </c>
       <c r="Q70">
-        <v>1.0767607442</v>
+        <v>1.07361751985</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.212385163900783</v>
+        <v>0.2174716424306942</v>
       </c>
       <c r="T70">
-        <v>2.171163129315693</v>
+        <v>2.237456995969847</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.289154749644262</v>
+        <v>5.212500332982751</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09984965915351518</v>
+        <v>0.09977266585877981</v>
       </c>
       <c r="C71">
-        <v>2.586730823745745</v>
+        <v>2.52582252536535</v>
       </c>
       <c r="D71">
-        <v>6.804760823745745</v>
+        <v>6.81072252536535</v>
       </c>
       <c r="E71">
-        <v>3.807030000000001</v>
+        <v>3.8739</v>
       </c>
       <c r="F71">
-        <v>4.614030000000001</v>
+        <v>4.6809</v>
       </c>
       <c r="G71">
         <v>0.396</v>
@@ -7109,28 +7109,28 @@
         <v>1.33</v>
       </c>
       <c r="M71">
-        <v>0.255155859</v>
+        <v>0.25885377</v>
       </c>
       <c r="N71">
-        <v>1.074844141</v>
+        <v>1.07114623</v>
       </c>
       <c r="O71">
-        <v>0.16122662115</v>
+        <v>0.1606719345</v>
       </c>
       <c r="P71">
-        <v>0.9136175198500001</v>
+        <v>0.9104742955</v>
       </c>
       <c r="Q71">
-        <v>1.07361751985</v>
+        <v>1.0704742955</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2174716424306942</v>
+        <v>0.2228972195292661</v>
       </c>
       <c r="T71">
-        <v>2.237456995969847</v>
+        <v>2.308170453734279</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.212500332982751</v>
+        <v>5.138036042511569</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09977266585877981</v>
+        <v>0.09969567256404442</v>
       </c>
       <c r="C72">
-        <v>2.52582252536535</v>
+        <v>2.464924682327307</v>
       </c>
       <c r="D72">
-        <v>6.81072252536535</v>
+        <v>6.816694682327308</v>
       </c>
       <c r="E72">
-        <v>3.8739</v>
+        <v>3.940770000000001</v>
       </c>
       <c r="F72">
-        <v>4.6809</v>
+        <v>4.747770000000001</v>
       </c>
       <c r="G72">
         <v>0.396</v>
@@ -7191,28 +7191,28 @@
         <v>1.33</v>
       </c>
       <c r="M72">
-        <v>0.25885377</v>
+        <v>0.262551681</v>
       </c>
       <c r="N72">
-        <v>1.07114623</v>
+        <v>1.067448319</v>
       </c>
       <c r="O72">
-        <v>0.1606719345</v>
+        <v>0.16011724785</v>
       </c>
       <c r="P72">
-        <v>0.9104742955</v>
+        <v>0.90733107115</v>
       </c>
       <c r="Q72">
-        <v>1.0704742955</v>
+        <v>1.06733107115</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2228972195292661</v>
+        <v>0.2286969743587739</v>
       </c>
       <c r="T72">
-        <v>2.308170453734279</v>
+        <v>2.38376070168936</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.138036042511569</v>
+        <v>5.065669337687462</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09969567256404441</v>
+        <v>0.09961867926930904</v>
       </c>
       <c r="C73">
-        <v>2.464924682327308</v>
+        <v>2.404037322159862</v>
       </c>
       <c r="D73">
-        <v>6.816694682327308</v>
+        <v>6.822677322159862</v>
       </c>
       <c r="E73">
-        <v>3.94077</v>
+        <v>4.007639999999999</v>
       </c>
       <c r="F73">
-        <v>4.74777</v>
+        <v>4.81464</v>
       </c>
       <c r="G73">
         <v>0.396</v>
@@ -7273,28 +7273,28 @@
         <v>1.33</v>
       </c>
       <c r="M73">
-        <v>0.262551681</v>
+        <v>0.266249592</v>
       </c>
       <c r="N73">
-        <v>1.067448319</v>
+        <v>1.063750408</v>
       </c>
       <c r="O73">
-        <v>0.16011724785</v>
+        <v>0.1595625612</v>
       </c>
       <c r="P73">
-        <v>0.90733107115</v>
+        <v>0.9041878468000002</v>
       </c>
       <c r="Q73">
-        <v>1.06733107115</v>
+        <v>1.0641878468</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2286969743587738</v>
+        <v>0.2349109973903894</v>
       </c>
       <c r="T73">
-        <v>2.383760701689359</v>
+        <v>2.464750253069803</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.065669337687462</v>
+        <v>4.995312819108472</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09961867926930904</v>
+        <v>0.09954168597457363</v>
       </c>
       <c r="C74">
-        <v>2.404037322159862</v>
+        <v>2.343160472487984</v>
       </c>
       <c r="D74">
-        <v>6.822677322159862</v>
+        <v>6.828670472487985</v>
       </c>
       <c r="E74">
-        <v>4.007639999999999</v>
+        <v>4.07451</v>
       </c>
       <c r="F74">
-        <v>4.81464</v>
+        <v>4.88151</v>
       </c>
       <c r="G74">
         <v>0.396</v>
@@ -7355,28 +7355,28 @@
         <v>1.33</v>
       </c>
       <c r="M74">
-        <v>0.266249592</v>
+        <v>0.269947503</v>
       </c>
       <c r="N74">
-        <v>1.063750408</v>
+        <v>1.060052497</v>
       </c>
       <c r="O74">
-        <v>0.1595625612</v>
+        <v>0.15900787455</v>
       </c>
       <c r="P74">
-        <v>0.9041878468000002</v>
+        <v>0.9010446224500001</v>
       </c>
       <c r="Q74">
-        <v>1.0641878468</v>
+        <v>1.06104462245</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2349109973903894</v>
+        <v>0.2415853184243468</v>
       </c>
       <c r="T74">
-        <v>2.464750253069803</v>
+        <v>2.551739030478429</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.995312819108472</v>
+        <v>4.926883876380956</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09954168597457363</v>
+        <v>0.09946469267983826</v>
       </c>
       <c r="C75">
-        <v>2.343160472487984</v>
+        <v>2.282294161033791</v>
       </c>
       <c r="D75">
-        <v>6.828670472487985</v>
+        <v>6.834674161033791</v>
       </c>
       <c r="E75">
-        <v>4.07451</v>
+        <v>4.14138</v>
       </c>
       <c r="F75">
-        <v>4.88151</v>
+        <v>4.94838</v>
       </c>
       <c r="G75">
         <v>0.396</v>
@@ -7437,28 +7437,28 @@
         <v>1.33</v>
       </c>
       <c r="M75">
-        <v>0.269947503</v>
+        <v>0.273645414</v>
       </c>
       <c r="N75">
-        <v>1.060052497</v>
+        <v>1.056354586</v>
       </c>
       <c r="O75">
-        <v>0.15900787455</v>
+        <v>0.1584531879</v>
       </c>
       <c r="P75">
-        <v>0.9010446224500001</v>
+        <v>0.8979013981000001</v>
       </c>
       <c r="Q75">
-        <v>1.06104462245</v>
+        <v>1.0579013981</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2415853184243468</v>
+        <v>0.2487730487686087</v>
       </c>
       <c r="T75">
-        <v>2.551739030478429</v>
+        <v>2.645419252303102</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.926883876380956</v>
+        <v>4.860304364537971</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09946469267983826</v>
+        <v>0.09938769938510288</v>
       </c>
       <c r="C76">
-        <v>2.282294161033791</v>
+        <v>2.221438415616988</v>
       </c>
       <c r="D76">
-        <v>6.834674161033791</v>
+        <v>6.840688415616988</v>
       </c>
       <c r="E76">
-        <v>4.14138</v>
+        <v>4.20825</v>
       </c>
       <c r="F76">
-        <v>4.94838</v>
+        <v>5.01525</v>
       </c>
       <c r="G76">
         <v>0.396</v>
@@ -7519,28 +7519,28 @@
         <v>1.33</v>
       </c>
       <c r="M76">
-        <v>0.273645414</v>
+        <v>0.277343325</v>
       </c>
       <c r="N76">
-        <v>1.056354586</v>
+        <v>1.052656675</v>
       </c>
       <c r="O76">
-        <v>0.1584531879</v>
+        <v>0.15789850125</v>
       </c>
       <c r="P76">
-        <v>0.8979013981000001</v>
+        <v>0.8947581737500001</v>
       </c>
       <c r="Q76">
-        <v>1.0579013981</v>
+        <v>1.05475817375</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2487730487686087</v>
+        <v>0.2565357975404115</v>
       </c>
       <c r="T76">
-        <v>2.645419252303102</v>
+        <v>2.74659389187375</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.860304364537971</v>
+        <v>4.795500306344131</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09938769938510288</v>
+        <v>0.0993107060903675</v>
       </c>
       <c r="C77">
-        <v>2.221438415616988</v>
+        <v>2.160593264155272</v>
       </c>
       <c r="D77">
-        <v>6.840688415616988</v>
+        <v>6.846713264155273</v>
       </c>
       <c r="E77">
-        <v>4.20825</v>
+        <v>4.27512</v>
       </c>
       <c r="F77">
-        <v>5.01525</v>
+        <v>5.082120000000001</v>
       </c>
       <c r="G77">
         <v>0.396</v>
@@ -7601,28 +7601,28 @@
         <v>1.33</v>
       </c>
       <c r="M77">
-        <v>0.277343325</v>
+        <v>0.281041236</v>
       </c>
       <c r="N77">
-        <v>1.052656675</v>
+        <v>1.048958764</v>
       </c>
       <c r="O77">
-        <v>0.15789850125</v>
+        <v>0.1573438146</v>
       </c>
       <c r="P77">
-        <v>0.8947581737500001</v>
+        <v>0.8916149494</v>
       </c>
       <c r="Q77">
-        <v>1.05475817375</v>
+        <v>1.0516149494</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2565357975404115</v>
+        <v>0.2649454420431979</v>
       </c>
       <c r="T77">
-        <v>2.74659389187375</v>
+        <v>2.856199751408618</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.795500306344131</v>
+        <v>4.732401618102761</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0993107060903675</v>
+        <v>0.0992337127956321</v>
       </c>
       <c r="C78">
-        <v>2.160593264155272</v>
+        <v>2.099758734664795</v>
       </c>
       <c r="D78">
-        <v>6.846713264155273</v>
+        <v>6.852748734664796</v>
       </c>
       <c r="E78">
-        <v>4.27512</v>
+        <v>4.34199</v>
       </c>
       <c r="F78">
-        <v>5.082120000000001</v>
+        <v>5.14899</v>
       </c>
       <c r="G78">
         <v>0.396</v>
@@ -7683,28 +7683,28 @@
         <v>1.33</v>
       </c>
       <c r="M78">
-        <v>0.281041236</v>
+        <v>0.284739147</v>
       </c>
       <c r="N78">
-        <v>1.048958764</v>
+        <v>1.045260853</v>
       </c>
       <c r="O78">
-        <v>0.1573438146</v>
+        <v>0.15678912795</v>
       </c>
       <c r="P78">
-        <v>0.8916149494</v>
+        <v>0.88847172505</v>
       </c>
       <c r="Q78">
-        <v>1.0516149494</v>
+        <v>1.04847172505</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2649454420431979</v>
+        <v>0.2740863599810092</v>
       </c>
       <c r="T78">
-        <v>2.856199751408618</v>
+        <v>2.975336555250866</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.732401618102761</v>
+        <v>4.6709418568287</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0992337127956321</v>
+        <v>0.0991567195008967</v>
       </c>
       <c r="C79">
-        <v>2.099758734664795</v>
+        <v>2.038934855260575</v>
       </c>
       <c r="D79">
-        <v>6.852748734664796</v>
+        <v>6.858794855260575</v>
       </c>
       <c r="E79">
-        <v>4.34199</v>
+        <v>4.40886</v>
       </c>
       <c r="F79">
-        <v>5.14899</v>
+        <v>5.21586</v>
       </c>
       <c r="G79">
         <v>0.396</v>
@@ -7765,28 +7765,28 @@
         <v>1.33</v>
       </c>
       <c r="M79">
-        <v>0.284739147</v>
+        <v>0.288437058</v>
       </c>
       <c r="N79">
-        <v>1.045260853</v>
+        <v>1.041562942</v>
       </c>
       <c r="O79">
-        <v>0.15678912795</v>
+        <v>0.1562344413</v>
       </c>
       <c r="P79">
-        <v>0.88847172505</v>
+        <v>0.8853285007000001</v>
       </c>
       <c r="Q79">
-        <v>1.04847172505</v>
+        <v>1.0453285007</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2740863599810092</v>
+        <v>0.2840582704586214</v>
       </c>
       <c r="T79">
-        <v>2.975336555250866</v>
+        <v>3.105303977624227</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.6709418568287</v>
+        <v>4.611057986869357</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0991567195008967</v>
+        <v>0.09907972620616132</v>
       </c>
       <c r="C80">
-        <v>2.038934855260575</v>
+        <v>1.978121654156934</v>
       </c>
       <c r="D80">
-        <v>6.858794855260575</v>
+        <v>6.864851654156935</v>
       </c>
       <c r="E80">
-        <v>4.40886</v>
+        <v>4.47573</v>
       </c>
       <c r="F80">
-        <v>5.21586</v>
+        <v>5.282730000000001</v>
       </c>
       <c r="G80">
         <v>0.396</v>
@@ -7847,28 +7847,28 @@
         <v>1.33</v>
       </c>
       <c r="M80">
-        <v>0.288437058</v>
+        <v>0.2921349690000001</v>
       </c>
       <c r="N80">
-        <v>1.041562942</v>
+        <v>1.037865031</v>
       </c>
       <c r="O80">
-        <v>0.1562344413</v>
+        <v>0.15567975465</v>
       </c>
       <c r="P80">
-        <v>0.8853285007000001</v>
+        <v>0.88218527635</v>
       </c>
       <c r="Q80">
-        <v>1.0453285007</v>
+        <v>1.04218527635</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2840582704586214</v>
+        <v>0.2949798866960063</v>
       </c>
       <c r="T80">
-        <v>3.105303977624227</v>
+        <v>3.247649249747432</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.611057986869357</v>
+        <v>4.552690164250757</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09907972620616132</v>
+        <v>0.100702732911426</v>
       </c>
       <c r="C81">
-        <v>1.978121654156934</v>
+        <v>1.78579784713079</v>
       </c>
       <c r="D81">
-        <v>6.864851654156935</v>
+        <v>6.739397847130791</v>
       </c>
       <c r="E81">
-        <v>4.47573</v>
+        <v>4.5426</v>
       </c>
       <c r="F81">
-        <v>5.282730000000001</v>
+        <v>5.349600000000001</v>
       </c>
       <c r="G81">
         <v>0.396</v>
@@ -7929,45 +7929,45 @@
         <v>1.33</v>
       </c>
       <c r="M81">
-        <v>0.2921349690000001</v>
+        <v>0.3092068800000001</v>
       </c>
       <c r="N81">
-        <v>1.037865031</v>
+        <v>1.02079312</v>
       </c>
       <c r="O81">
-        <v>0.15567975465</v>
+        <v>0.153118968</v>
       </c>
       <c r="P81">
-        <v>0.88218527635</v>
+        <v>0.867674152</v>
       </c>
       <c r="Q81">
-        <v>1.04218527635</v>
+        <v>1.027674152</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2949798866960063</v>
+        <v>0.3069936645571298</v>
       </c>
       <c r="T81">
-        <v>3.247649249747432</v>
+        <v>3.404229049082958</v>
       </c>
       <c r="U81">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V81">
         <v>0.15</v>
       </c>
       <c r="W81">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y81">
-        <v>4.552690164250757</v>
+        <v>4.301327318460701</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.100702732911426</v>
+        <v>0.1006469896166906</v>
       </c>
       <c r="C82">
-        <v>1.78579784713079</v>
+        <v>1.723160559706301</v>
       </c>
       <c r="D82">
-        <v>6.739397847130791</v>
+        <v>6.743630559706301</v>
       </c>
       <c r="E82">
-        <v>4.5426</v>
+        <v>4.60947</v>
       </c>
       <c r="F82">
-        <v>5.349600000000001</v>
+        <v>5.41647</v>
       </c>
       <c r="G82">
         <v>0.396</v>
@@ -8011,28 +8011,28 @@
         <v>1.33</v>
       </c>
       <c r="M82">
-        <v>0.3092068800000001</v>
+        <v>0.313071966</v>
       </c>
       <c r="N82">
-        <v>1.02079312</v>
+        <v>1.016928034</v>
       </c>
       <c r="O82">
-        <v>0.153118968</v>
+        <v>0.1525392051</v>
       </c>
       <c r="P82">
-        <v>0.867674152</v>
+        <v>0.8643888289</v>
       </c>
       <c r="Q82">
-        <v>1.027674152</v>
+        <v>1.0243888289</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3069936645571298</v>
+        <v>0.320272050614161</v>
       </c>
       <c r="T82">
-        <v>3.404229049082958</v>
+        <v>3.577290932559066</v>
       </c>
       <c r="U82">
         <v>0.0578</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.301327318460701</v>
+        <v>4.248224512059952</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1006469896166906</v>
+        <v>0.1005912463219552</v>
       </c>
       <c r="C83">
-        <v>1.723160559706301</v>
+        <v>1.660528592375794</v>
       </c>
       <c r="D83">
-        <v>6.743630559706301</v>
+        <v>6.747868592375795</v>
       </c>
       <c r="E83">
-        <v>4.60947</v>
+        <v>4.676340000000001</v>
       </c>
       <c r="F83">
-        <v>5.41647</v>
+        <v>5.483340000000001</v>
       </c>
       <c r="G83">
         <v>0.396</v>
@@ -8093,28 +8093,28 @@
         <v>1.33</v>
       </c>
       <c r="M83">
-        <v>0.313071966</v>
+        <v>0.3169370520000001</v>
       </c>
       <c r="N83">
-        <v>1.016928034</v>
+        <v>1.013062948</v>
       </c>
       <c r="O83">
-        <v>0.1525392051</v>
+        <v>0.1519594422</v>
       </c>
       <c r="P83">
-        <v>0.8643888289</v>
+        <v>0.8611035057999999</v>
       </c>
       <c r="Q83">
-        <v>1.0243888289</v>
+        <v>1.0211035058</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.320272050614161</v>
+        <v>0.3350258128997511</v>
       </c>
       <c r="T83">
-        <v>3.577290932559066</v>
+        <v>3.769581914199185</v>
       </c>
       <c r="U83">
         <v>0.0578</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.248224512059952</v>
+        <v>4.196416896059221</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1005912463219552</v>
+        <v>0.1005355030272198</v>
       </c>
       <c r="C84">
-        <v>1.660528592375794</v>
+        <v>1.597901955175809</v>
       </c>
       <c r="D84">
-        <v>6.747868592375795</v>
+        <v>6.75211195517581</v>
       </c>
       <c r="E84">
-        <v>4.676340000000001</v>
+        <v>4.74321</v>
       </c>
       <c r="F84">
-        <v>5.483340000000001</v>
+        <v>5.550210000000001</v>
       </c>
       <c r="G84">
         <v>0.396</v>
@@ -8175,28 +8175,28 @@
         <v>1.33</v>
       </c>
       <c r="M84">
-        <v>0.3169370520000001</v>
+        <v>0.3208021380000001</v>
       </c>
       <c r="N84">
-        <v>1.013062948</v>
+        <v>1.009197862</v>
       </c>
       <c r="O84">
-        <v>0.1519594422</v>
+        <v>0.1513796793</v>
       </c>
       <c r="P84">
-        <v>0.8611035057999999</v>
+        <v>0.8578181827</v>
       </c>
       <c r="Q84">
-        <v>1.0211035058</v>
+        <v>1.0178181827</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3350258128997511</v>
+        <v>0.3515153119248224</v>
       </c>
       <c r="T84">
-        <v>3.769581914199185</v>
+        <v>3.984495364267554</v>
       </c>
       <c r="U84">
         <v>0.0578</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.196416896059221</v>
+        <v>4.145857656347664</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1005355030272198</v>
+        <v>0.1004797597324844</v>
       </c>
       <c r="C85">
-        <v>1.597901955175809</v>
+        <v>1.53528065816815</v>
       </c>
       <c r="D85">
-        <v>6.75211195517581</v>
+        <v>6.756360658168151</v>
       </c>
       <c r="E85">
-        <v>4.74321</v>
+        <v>4.81008</v>
       </c>
       <c r="F85">
-        <v>5.550210000000001</v>
+        <v>5.617080000000001</v>
       </c>
       <c r="G85">
         <v>0.396</v>
@@ -8257,28 +8257,28 @@
         <v>1.33</v>
       </c>
       <c r="M85">
-        <v>0.3208021380000001</v>
+        <v>0.324667224</v>
       </c>
       <c r="N85">
-        <v>1.009197862</v>
+        <v>1.005332776</v>
       </c>
       <c r="O85">
-        <v>0.1513796793</v>
+        <v>0.1507999164</v>
       </c>
       <c r="P85">
-        <v>0.8578181827</v>
+        <v>0.8545328595999999</v>
       </c>
       <c r="Q85">
-        <v>1.0178181827</v>
+        <v>1.0145328596</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3515153119248224</v>
+        <v>0.3700659983280278</v>
       </c>
       <c r="T85">
-        <v>3.984495364267554</v>
+        <v>4.22627299559447</v>
       </c>
       <c r="U85">
         <v>0.0578</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.145857656347664</v>
+        <v>4.09650220805781</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1004797597324844</v>
+        <v>0.100424016437749</v>
       </c>
       <c r="C86">
-        <v>1.535280658168151</v>
+        <v>1.472664711439964</v>
       </c>
       <c r="D86">
-        <v>6.756360658168151</v>
+        <v>6.760614711439964</v>
       </c>
       <c r="E86">
-        <v>4.810079999999999</v>
+        <v>4.87695</v>
       </c>
       <c r="F86">
-        <v>5.61708</v>
+        <v>5.68395</v>
       </c>
       <c r="G86">
         <v>0.396</v>
@@ -8339,28 +8339,28 @@
         <v>1.33</v>
       </c>
       <c r="M86">
-        <v>0.324667224</v>
+        <v>0.32853231</v>
       </c>
       <c r="N86">
-        <v>1.005332776</v>
+        <v>1.00146769</v>
       </c>
       <c r="O86">
-        <v>0.1507999164</v>
+        <v>0.1502201535</v>
       </c>
       <c r="P86">
-        <v>0.8545328596000001</v>
+        <v>0.8512475365000001</v>
       </c>
       <c r="Q86">
-        <v>1.0145328596</v>
+        <v>1.0112475365</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3700659983280276</v>
+        <v>0.3910901095849935</v>
       </c>
       <c r="T86">
-        <v>4.226272995594467</v>
+        <v>4.500287644431637</v>
       </c>
       <c r="U86">
         <v>0.0578</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.096502208057812</v>
+        <v>4.048308064433602</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.100424016437749</v>
+        <v>0.1003682731430136</v>
       </c>
       <c r="C87">
-        <v>1.472664711439964</v>
+        <v>1.410054125103815</v>
       </c>
       <c r="D87">
-        <v>6.760614711439964</v>
+        <v>6.764874125103815</v>
       </c>
       <c r="E87">
-        <v>4.87695</v>
+        <v>4.94382</v>
       </c>
       <c r="F87">
-        <v>5.68395</v>
+        <v>5.75082</v>
       </c>
       <c r="G87">
         <v>0.396</v>
@@ -8421,28 +8421,28 @@
         <v>1.33</v>
       </c>
       <c r="M87">
-        <v>0.32853231</v>
+        <v>0.332397396</v>
       </c>
       <c r="N87">
-        <v>1.00146769</v>
+        <v>0.9976026040000001</v>
       </c>
       <c r="O87">
-        <v>0.1502201535</v>
+        <v>0.1496403906</v>
       </c>
       <c r="P87">
-        <v>0.8512475365000001</v>
+        <v>0.8479622134000001</v>
       </c>
       <c r="Q87">
-        <v>1.0112475365</v>
+        <v>1.0079622134</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3910901095849935</v>
+        <v>0.4151176653072402</v>
       </c>
       <c r="T87">
-        <v>4.500287644431637</v>
+        <v>4.813447243102687</v>
       </c>
       <c r="U87">
         <v>0.0578</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.048308064433602</v>
+        <v>4.001234714847165</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1003682731430136</v>
+        <v>0.1029007798482783</v>
       </c>
       <c r="C88">
-        <v>1.410054125103815</v>
+        <v>1.154938490928867</v>
       </c>
       <c r="D88">
-        <v>6.764874125103815</v>
+        <v>6.576628490928867</v>
       </c>
       <c r="E88">
-        <v>4.94382</v>
+        <v>5.010689999999999</v>
       </c>
       <c r="F88">
-        <v>5.75082</v>
+        <v>5.81769</v>
       </c>
       <c r="G88">
         <v>0.396</v>
@@ -8503,45 +8503,45 @@
         <v>1.33</v>
       </c>
       <c r="M88">
-        <v>0.332397396</v>
+        <v>0.356624397</v>
       </c>
       <c r="N88">
-        <v>0.9976026040000001</v>
+        <v>0.973375603</v>
       </c>
       <c r="O88">
-        <v>0.1496403906</v>
+        <v>0.14600634045</v>
       </c>
       <c r="P88">
-        <v>0.8479622134000001</v>
+        <v>0.82736926255</v>
       </c>
       <c r="Q88">
-        <v>1.0079622134</v>
+        <v>0.9873692625499999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4151176653072402</v>
+        <v>0.4428417680636788</v>
       </c>
       <c r="T88">
-        <v>4.813447243102687</v>
+        <v>5.174785241569285</v>
       </c>
       <c r="U88">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V88">
         <v>0.15</v>
       </c>
       <c r="W88">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y88">
-        <v>4.001234714847165</v>
+        <v>3.729413946965608</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1029007798482783</v>
+        <v>0.1028747865535429</v>
       </c>
       <c r="C89">
-        <v>1.154938490928867</v>
+        <v>1.089947389286948</v>
       </c>
       <c r="D89">
-        <v>6.576628490928867</v>
+        <v>6.578507389286949</v>
       </c>
       <c r="E89">
-        <v>5.010689999999999</v>
+        <v>5.07756</v>
       </c>
       <c r="F89">
-        <v>5.81769</v>
+        <v>5.88456</v>
       </c>
       <c r="G89">
         <v>0.396</v>
@@ -8585,28 +8585,28 @@
         <v>1.33</v>
       </c>
       <c r="M89">
-        <v>0.356624397</v>
+        <v>0.360723528</v>
       </c>
       <c r="N89">
-        <v>0.973375603</v>
+        <v>0.969276472</v>
       </c>
       <c r="O89">
-        <v>0.14600634045</v>
+        <v>0.1453914708</v>
       </c>
       <c r="P89">
-        <v>0.82736926255</v>
+        <v>0.8238850012</v>
       </c>
       <c r="Q89">
-        <v>0.9873692625499999</v>
+        <v>0.9838850011999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4428417680636788</v>
+        <v>0.4751865546128572</v>
       </c>
       <c r="T89">
-        <v>5.174785241569285</v>
+        <v>5.596346239780317</v>
       </c>
       <c r="U89">
         <v>0.0613</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.729413946965608</v>
+        <v>3.687034243022817</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1028747865535429</v>
+        <v>0.1028487932588075</v>
       </c>
       <c r="C90">
-        <v>1.089947389286948</v>
+        <v>1.024957361528988</v>
       </c>
       <c r="D90">
-        <v>6.578507389286949</v>
+        <v>6.580387361528988</v>
       </c>
       <c r="E90">
-        <v>5.07756</v>
+        <v>5.14443</v>
       </c>
       <c r="F90">
-        <v>5.88456</v>
+        <v>5.95143</v>
       </c>
       <c r="G90">
         <v>0.396</v>
@@ -8667,28 +8667,28 @@
         <v>1.33</v>
       </c>
       <c r="M90">
-        <v>0.360723528</v>
+        <v>0.364822659</v>
       </c>
       <c r="N90">
-        <v>0.969276472</v>
+        <v>0.9651773410000001</v>
       </c>
       <c r="O90">
-        <v>0.1453914708</v>
+        <v>0.14477660115</v>
       </c>
       <c r="P90">
-        <v>0.8238850012</v>
+        <v>0.8204007398500001</v>
       </c>
       <c r="Q90">
-        <v>0.9838850011999999</v>
+        <v>0.98040073985</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4751865546128572</v>
+        <v>0.5134122114437044</v>
       </c>
       <c r="T90">
-        <v>5.596346239780317</v>
+        <v>6.094554692211535</v>
       </c>
       <c r="U90">
         <v>0.0613</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.687034243022817</v>
+        <v>3.645606891977617</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1028487932588075</v>
+        <v>0.1028227999640721</v>
       </c>
       <c r="C91">
-        <v>1.024957361528988</v>
+        <v>0.9599684085759064</v>
       </c>
       <c r="D91">
-        <v>6.580387361528988</v>
+        <v>6.582268408575906</v>
       </c>
       <c r="E91">
-        <v>5.14443</v>
+        <v>5.2113</v>
       </c>
       <c r="F91">
-        <v>5.95143</v>
+        <v>6.0183</v>
       </c>
       <c r="G91">
         <v>0.396</v>
@@ -8749,28 +8749,28 @@
         <v>1.33</v>
       </c>
       <c r="M91">
-        <v>0.364822659</v>
+        <v>0.36892179</v>
       </c>
       <c r="N91">
-        <v>0.9651773410000001</v>
+        <v>0.96107821</v>
       </c>
       <c r="O91">
-        <v>0.14477660115</v>
+        <v>0.1441617315</v>
       </c>
       <c r="P91">
-        <v>0.8204007398500001</v>
+        <v>0.8169164785</v>
       </c>
       <c r="Q91">
-        <v>0.98040073985</v>
+        <v>0.9769164785</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5134122114437044</v>
+        <v>0.559282999640721</v>
       </c>
       <c r="T91">
-        <v>6.094554692211535</v>
+        <v>6.692404835128998</v>
       </c>
       <c r="U91">
         <v>0.0613</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.645606891977617</v>
+        <v>3.605100148733421</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1028227999640721</v>
+        <v>0.1027968066693367</v>
       </c>
       <c r="C92">
-        <v>0.9599684085759064</v>
+        <v>0.8949805313496908</v>
       </c>
       <c r="D92">
-        <v>6.582268408575906</v>
+        <v>6.584150531349692</v>
       </c>
       <c r="E92">
-        <v>5.2113</v>
+        <v>5.27817</v>
       </c>
       <c r="F92">
-        <v>6.0183</v>
+        <v>6.085170000000001</v>
       </c>
       <c r="G92">
         <v>0.396</v>
@@ -8831,28 +8831,28 @@
         <v>1.33</v>
       </c>
       <c r="M92">
-        <v>0.36892179</v>
+        <v>0.3730209210000001</v>
       </c>
       <c r="N92">
-        <v>0.96107821</v>
+        <v>0.956979079</v>
       </c>
       <c r="O92">
-        <v>0.1441617315</v>
+        <v>0.14354686185</v>
       </c>
       <c r="P92">
-        <v>0.8169164785</v>
+        <v>0.81343221715</v>
       </c>
       <c r="Q92">
-        <v>0.9769164785</v>
+        <v>0.9734322171499999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.559282999640721</v>
+        <v>0.6153472963259636</v>
       </c>
       <c r="T92">
-        <v>6.692404835128998</v>
+        <v>7.423110565361451</v>
       </c>
       <c r="U92">
         <v>0.0613</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.605100148733421</v>
+        <v>3.565483663582504</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1027968066693367</v>
+        <v>0.1027708133746013</v>
       </c>
       <c r="C93">
-        <v>0.8949805313496908</v>
+        <v>0.829993730773384</v>
       </c>
       <c r="D93">
-        <v>6.584150531349692</v>
+        <v>6.586033730773384</v>
       </c>
       <c r="E93">
-        <v>5.27817</v>
+        <v>5.34504</v>
       </c>
       <c r="F93">
-        <v>6.085170000000001</v>
+        <v>6.15204</v>
       </c>
       <c r="G93">
         <v>0.396</v>
@@ -8913,28 +8913,28 @@
         <v>1.33</v>
       </c>
       <c r="M93">
-        <v>0.3730209210000001</v>
+        <v>0.377120052</v>
       </c>
       <c r="N93">
-        <v>0.956979079</v>
+        <v>0.9528799480000001</v>
       </c>
       <c r="O93">
-        <v>0.14354686185</v>
+        <v>0.1429319922</v>
       </c>
       <c r="P93">
-        <v>0.81343221715</v>
+        <v>0.8099479558000001</v>
       </c>
       <c r="Q93">
-        <v>0.9734322171499999</v>
+        <v>0.9699479558</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6153472963259636</v>
+        <v>0.6854276671825169</v>
       </c>
       <c r="T93">
-        <v>7.423110565361451</v>
+        <v>8.33649272815202</v>
       </c>
       <c r="U93">
         <v>0.0613</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.565483663582504</v>
+        <v>3.526728406369651</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1027708133746013</v>
+        <v>0.1049582200798659</v>
       </c>
       <c r="C94">
-        <v>0.829993730773384</v>
+        <v>0.608327870544521</v>
       </c>
       <c r="D94">
-        <v>6.586033730773384</v>
+        <v>6.431237870544521</v>
       </c>
       <c r="E94">
-        <v>5.34504</v>
+        <v>5.41191</v>
       </c>
       <c r="F94">
-        <v>6.15204</v>
+        <v>6.21891</v>
       </c>
       <c r="G94">
         <v>0.396</v>
@@ -8995,45 +8995,45 @@
         <v>1.33</v>
       </c>
       <c r="M94">
-        <v>0.377120052</v>
+        <v>0.3986321310000001</v>
       </c>
       <c r="N94">
-        <v>0.9528799480000001</v>
+        <v>0.931367869</v>
       </c>
       <c r="O94">
-        <v>0.1429319922</v>
+        <v>0.13970518035</v>
       </c>
       <c r="P94">
-        <v>0.8099479558000001</v>
+        <v>0.79166268865</v>
       </c>
       <c r="Q94">
-        <v>0.9699479558</v>
+        <v>0.9516626886499999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6854276671825169</v>
+        <v>0.7755310011409425</v>
       </c>
       <c r="T94">
-        <v>8.33649272815202</v>
+        <v>9.510841223168464</v>
       </c>
       <c r="U94">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V94">
         <v>0.15</v>
       </c>
       <c r="W94">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y94">
-        <v>3.526728406369651</v>
+        <v>3.336409427568195</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1049582200798659</v>
+        <v>0.1049560267851306</v>
       </c>
       <c r="C95">
-        <v>0.608327870544521</v>
+        <v>0.5416094385921975</v>
       </c>
       <c r="D95">
-        <v>6.431237870544521</v>
+        <v>6.431389438592198</v>
       </c>
       <c r="E95">
-        <v>5.41191</v>
+        <v>5.47878</v>
       </c>
       <c r="F95">
-        <v>6.21891</v>
+        <v>6.285780000000001</v>
       </c>
       <c r="G95">
         <v>0.396</v>
@@ -9077,28 +9077,28 @@
         <v>1.33</v>
       </c>
       <c r="M95">
-        <v>0.3986321310000001</v>
+        <v>0.4029184980000001</v>
       </c>
       <c r="N95">
-        <v>0.931367869</v>
+        <v>0.9270815020000001</v>
       </c>
       <c r="O95">
-        <v>0.13970518035</v>
+        <v>0.1390622253</v>
       </c>
       <c r="P95">
-        <v>0.79166268865</v>
+        <v>0.7880192767</v>
       </c>
       <c r="Q95">
-        <v>0.9516626886499999</v>
+        <v>0.9480192767</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7755310011409425</v>
+        <v>0.8956687797521766</v>
       </c>
       <c r="T95">
-        <v>9.510841223168464</v>
+        <v>11.07663921652372</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.336409427568195</v>
+        <v>3.30091571025364</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1049560267851306</v>
+        <v>0.1049538334903952</v>
       </c>
       <c r="C96">
-        <v>0.5416094385921975</v>
+        <v>0.4748910137841946</v>
       </c>
       <c r="D96">
-        <v>6.431389438592198</v>
+        <v>6.431541013784195</v>
       </c>
       <c r="E96">
-        <v>5.47878</v>
+        <v>5.54565</v>
       </c>
       <c r="F96">
-        <v>6.285780000000001</v>
+        <v>6.352650000000001</v>
       </c>
       <c r="G96">
         <v>0.396</v>
@@ -9159,28 +9159,28 @@
         <v>1.33</v>
       </c>
       <c r="M96">
-        <v>0.4029184980000001</v>
+        <v>0.4072048650000001</v>
       </c>
       <c r="N96">
-        <v>0.9270815020000001</v>
+        <v>0.922795135</v>
       </c>
       <c r="O96">
-        <v>0.1390622253</v>
+        <v>0.13841927025</v>
       </c>
       <c r="P96">
-        <v>0.7880192767</v>
+        <v>0.78437586475</v>
       </c>
       <c r="Q96">
-        <v>0.9480192767</v>
+        <v>0.9443758647499999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8956687797521766</v>
+        <v>1.063861669807905</v>
       </c>
       <c r="T96">
-        <v>11.07663921652372</v>
+        <v>13.26875640722109</v>
       </c>
       <c r="U96">
         <v>0.0641</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.30091571025364</v>
+        <v>3.266169229093075</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1049538334903952</v>
+        <v>0.1049516401956598</v>
       </c>
       <c r="C97">
-        <v>0.4748910137841946</v>
+        <v>0.4081725961210196</v>
       </c>
       <c r="D97">
-        <v>6.431541013784195</v>
+        <v>6.43169259612102</v>
       </c>
       <c r="E97">
-        <v>5.54565</v>
+        <v>5.61252</v>
       </c>
       <c r="F97">
-        <v>6.352650000000001</v>
+        <v>6.41952</v>
       </c>
       <c r="G97">
         <v>0.396</v>
@@ -9241,28 +9241,28 @@
         <v>1.33</v>
       </c>
       <c r="M97">
-        <v>0.4072048650000001</v>
+        <v>0.411491232</v>
       </c>
       <c r="N97">
-        <v>0.922795135</v>
+        <v>0.918508768</v>
       </c>
       <c r="O97">
-        <v>0.13841927025</v>
+        <v>0.1377763152</v>
       </c>
       <c r="P97">
-        <v>0.78437586475</v>
+        <v>0.7807324528</v>
       </c>
       <c r="Q97">
-        <v>0.9443758647499999</v>
+        <v>0.9407324528</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.063861669807905</v>
+        <v>1.316151004891497</v>
       </c>
       <c r="T97">
-        <v>13.26875640722109</v>
+        <v>16.55693219326714</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.266169229093075</v>
+        <v>3.232146632956689</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1049516401956598</v>
+        <v>0.1049494469009244</v>
       </c>
       <c r="C98">
-        <v>0.4081725961210179</v>
+        <v>0.3414541856031743</v>
       </c>
       <c r="D98">
-        <v>6.431692596121018</v>
+        <v>6.431844185603175</v>
       </c>
       <c r="E98">
-        <v>5.61252</v>
+        <v>5.67939</v>
       </c>
       <c r="F98">
-        <v>6.41952</v>
+        <v>6.48639</v>
       </c>
       <c r="G98">
         <v>0.396</v>
@@ -9323,28 +9323,28 @@
         <v>1.33</v>
       </c>
       <c r="M98">
-        <v>0.411491232</v>
+        <v>0.4157775990000001</v>
       </c>
       <c r="N98">
-        <v>0.918508768</v>
+        <v>0.914222401</v>
       </c>
       <c r="O98">
-        <v>0.1377763152</v>
+        <v>0.13713336015</v>
       </c>
       <c r="P98">
-        <v>0.7807324528</v>
+        <v>0.77708904085</v>
       </c>
       <c r="Q98">
-        <v>0.9407324528</v>
+        <v>0.9370890408499999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.316151004891494</v>
+        <v>1.736633230030812</v>
       </c>
       <c r="T98">
-        <v>16.5569321932671</v>
+        <v>22.03722517001049</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.232146632956689</v>
+        <v>3.198825533647857</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1049494469009244</v>
+        <v>0.104947253606189</v>
       </c>
       <c r="C99">
-        <v>0.3414541856031743</v>
+        <v>0.2747357822311658</v>
       </c>
       <c r="D99">
-        <v>6.431844185603175</v>
+        <v>6.431995782231166</v>
       </c>
       <c r="E99">
-        <v>5.67939</v>
+        <v>5.746259999999999</v>
       </c>
       <c r="F99">
-        <v>6.48639</v>
+        <v>6.55326</v>
       </c>
       <c r="G99">
         <v>0.396</v>
@@ -9405,28 +9405,28 @@
         <v>1.33</v>
       </c>
       <c r="M99">
-        <v>0.4157775990000001</v>
+        <v>0.420063966</v>
       </c>
       <c r="N99">
-        <v>0.914222401</v>
+        <v>0.909936034</v>
       </c>
       <c r="O99">
-        <v>0.13713336015</v>
+        <v>0.1364904051</v>
       </c>
       <c r="P99">
-        <v>0.77708904085</v>
+        <v>0.7734456289</v>
       </c>
       <c r="Q99">
-        <v>0.9370890408499999</v>
+        <v>0.9334456288999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.736633230030812</v>
+        <v>2.577597680309449</v>
       </c>
       <c r="T99">
-        <v>22.03722517001049</v>
+        <v>32.99781112349728</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.198825533647857</v>
+        <v>3.1661844567739</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.104947253606189</v>
+        <v>0.1049450603114536</v>
       </c>
       <c r="C100">
-        <v>0.2747357822311658</v>
+        <v>0.2080173860055012</v>
       </c>
       <c r="D100">
-        <v>6.431995782231166</v>
+        <v>6.432147386005502</v>
       </c>
       <c r="E100">
-        <v>5.746259999999999</v>
+        <v>5.81313</v>
       </c>
       <c r="F100">
-        <v>6.55326</v>
+        <v>6.620130000000001</v>
       </c>
       <c r="G100">
         <v>0.396</v>
@@ -9487,28 +9487,28 @@
         <v>1.33</v>
       </c>
       <c r="M100">
-        <v>0.420063966</v>
+        <v>0.4243503330000001</v>
       </c>
       <c r="N100">
-        <v>0.909936034</v>
+        <v>0.905649667</v>
       </c>
       <c r="O100">
-        <v>0.1364904051</v>
+        <v>0.13584745005</v>
       </c>
       <c r="P100">
-        <v>0.7734456289</v>
+        <v>0.7698022169500001</v>
       </c>
       <c r="Q100">
-        <v>0.9334456288999999</v>
+        <v>0.92980221695</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.577597680309449</v>
+        <v>5.100491031145358</v>
       </c>
       <c r="T100">
-        <v>32.99781112349728</v>
+        <v>65.87956898395763</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.1661844567739</v>
+        <v>3.134202795594365</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1049450603114536</v>
-      </c>
-      <c r="C101">
-        <v>0.2080173860055012</v>
-      </c>
-      <c r="D101">
-        <v>6.432147386005502</v>
-      </c>
-      <c r="E101">
-        <v>5.81313</v>
-      </c>
-      <c r="F101">
-        <v>6.620130000000001</v>
-      </c>
-      <c r="G101">
-        <v>0.396</v>
-      </c>
-      <c r="H101">
-        <v>5.88</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.49</v>
-      </c>
-      <c r="K101">
-        <v>0.1599999999999999</v>
-      </c>
-      <c r="L101">
-        <v>1.33</v>
-      </c>
-      <c r="M101">
-        <v>0.4243503330000001</v>
-      </c>
-      <c r="N101">
-        <v>0.905649667</v>
-      </c>
-      <c r="O101">
-        <v>0.13584745005</v>
-      </c>
-      <c r="P101">
-        <v>0.7698022169500001</v>
-      </c>
-      <c r="Q101">
-        <v>0.92980221695</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.100491031145358</v>
-      </c>
-      <c r="T101">
-        <v>65.87956898395763</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.054485</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.134202795594365</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
